--- a/artfynd/A 17248-2026 artfynd.xlsx
+++ b/artfynd/A 17248-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136996334</v>
       </c>
       <c r="B2" t="n">
-        <v>89474</v>
+        <v>89476</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>136996333</v>
       </c>
       <c r="B3" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>136996220</v>
       </c>
       <c r="B4" t="n">
-        <v>80592</v>
+        <v>80596</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>136996284</v>
       </c>
       <c r="B22" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>136996285</v>
       </c>
       <c r="B23" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>136996286</v>
       </c>
       <c r="B24" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>136996287</v>
       </c>
       <c r="B25" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>136996288</v>
       </c>
       <c r="B26" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>136996289</v>
       </c>
       <c r="B27" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>136996290</v>
       </c>
       <c r="B28" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>136996292</v>
       </c>
       <c r="B29" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>136996293</v>
       </c>
       <c r="B30" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         <v>136996294</v>
       </c>
       <c r="B31" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>136996295</v>
       </c>
       <c r="B32" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>136996297</v>
       </c>
       <c r="B33" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4913,7 +4913,7 @@
         <v>136996298</v>
       </c>
       <c r="B34" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
         <v>136996299</v>
       </c>
       <c r="B35" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>136996300</v>
       </c>
       <c r="B36" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>136996301</v>
       </c>
       <c r="B37" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>136996302</v>
       </c>
       <c r="B38" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>136996303</v>
       </c>
       <c r="B39" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>136996304</v>
       </c>
       <c r="B40" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>136996305</v>
       </c>
       <c r="B41" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>136996306</v>
       </c>
       <c r="B42" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>136996307</v>
       </c>
       <c r="B43" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>136996308</v>
       </c>
       <c r="B44" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>136996309</v>
       </c>
       <c r="B45" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>136996310</v>
       </c>
       <c r="B46" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>136996311</v>
       </c>
       <c r="B47" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>136996313</v>
       </c>
       <c r="B48" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>136996314</v>
       </c>
       <c r="B49" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>136996315</v>
       </c>
       <c r="B50" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>136996316</v>
       </c>
       <c r="B51" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>136996317</v>
       </c>
       <c r="B52" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>136996318</v>
       </c>
       <c r="B53" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>136996319</v>
       </c>
       <c r="B54" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>136996320</v>
       </c>
       <c r="B55" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>136996321</v>
       </c>
       <c r="B56" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>136996322</v>
       </c>
       <c r="B57" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>136996323</v>
       </c>
       <c r="B58" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>136996324</v>
       </c>
       <c r="B59" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>136996325</v>
       </c>
       <c r="B60" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>136996326</v>
       </c>
       <c r="B61" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>136996332</v>
       </c>
       <c r="B62" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>136996223</v>
       </c>
       <c r="B65" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>136996224</v>
       </c>
       <c r="B66" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>136996225</v>
       </c>
       <c r="B67" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>136996226</v>
       </c>
       <c r="B68" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>136996228</v>
       </c>
       <c r="B69" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>136996229</v>
       </c>
       <c r="B70" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9891,7 +9891,7 @@
         <v>136996230</v>
       </c>
       <c r="B71" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>136996231</v>
       </c>
       <c r="B72" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>136996232</v>
       </c>
       <c r="B73" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>136996233</v>
       </c>
       <c r="B74" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>136996234</v>
       </c>
       <c r="B75" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>136996235</v>
       </c>
       <c r="B76" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>136996236</v>
       </c>
       <c r="B77" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>136996237</v>
       </c>
       <c r="B78" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10969,7 +10969,7 @@
         <v>136996239</v>
       </c>
       <c r="B79" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -11100,7 +11100,7 @@
         <v>136996240</v>
       </c>
       <c r="B80" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11235,7 +11235,7 @@
         <v>136996241</v>
       </c>
       <c r="B81" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -11371,7 +11371,7 @@
         <v>136996242</v>
       </c>
       <c r="B82" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>136996243</v>
       </c>
       <c r="B83" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11646,7 +11646,7 @@
         <v>136996244</v>
       </c>
       <c r="B84" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>136996245</v>
       </c>
       <c r="B85" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         <v>136996246</v>
       </c>
       <c r="B86" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>136996247</v>
       </c>
       <c r="B87" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         <v>136996248</v>
       </c>
       <c r="B88" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         <v>136996249</v>
       </c>
       <c r="B89" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>136996204</v>
       </c>
       <c r="B94" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -13114,7 +13114,7 @@
         <v>136996205</v>
       </c>
       <c r="B95" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -13249,7 +13249,7 @@
         <v>136996207</v>
       </c>
       <c r="B96" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>136996208</v>
       </c>
       <c r="B97" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
         <v>136996209</v>
       </c>
       <c r="B98" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>136996210</v>
       </c>
       <c r="B99" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13789,7 +13789,7 @@
         <v>136996211</v>
       </c>
       <c r="B100" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>136996212</v>
       </c>
       <c r="B101" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>136996213</v>
       </c>
       <c r="B102" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>136996214</v>
       </c>
       <c r="B103" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -14329,7 +14329,7 @@
         <v>136996215</v>
       </c>
       <c r="B104" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -14464,7 +14464,7 @@
         <v>136996216</v>
       </c>
       <c r="B105" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -14599,7 +14599,7 @@
         <v>136996218</v>
       </c>
       <c r="B106" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14734,7 +14734,7 @@
         <v>136996335</v>
       </c>
       <c r="B107" t="n">
-        <v>80602</v>
+        <v>80606</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>136996250</v>
       </c>
       <c r="B109" t="n">
-        <v>80603</v>
+        <v>80607</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>136996251</v>
       </c>
       <c r="B110" t="n">
-        <v>80603</v>
+        <v>80607</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>136996252</v>
       </c>
       <c r="B111" t="n">
-        <v>80603</v>
+        <v>80607</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         <v>136996253</v>
       </c>
       <c r="B112" t="n">
-        <v>80603</v>
+        <v>80607</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>136996254</v>
       </c>
       <c r="B113" t="n">
-        <v>80603</v>
+        <v>80607</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
         <v>136996255</v>
       </c>
       <c r="B114" t="n">
-        <v>80603</v>
+        <v>80607</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -15825,7 +15825,7 @@
         <v>136996256</v>
       </c>
       <c r="B115" t="n">
-        <v>80603</v>
+        <v>80607</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>136996257</v>
       </c>
       <c r="B116" t="n">
-        <v>80603</v>
+        <v>80607</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>136996258</v>
       </c>
       <c r="B117" t="n">
-        <v>80603</v>
+        <v>80607</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>136996259</v>
       </c>
       <c r="B118" t="n">
-        <v>80603</v>
+        <v>80607</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>136996260</v>
       </c>
       <c r="B119" t="n">
-        <v>80603</v>
+        <v>80607</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>136996261</v>
       </c>
       <c r="B120" t="n">
-        <v>80603</v>
+        <v>80607</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>136996262</v>
       </c>
       <c r="B121" t="n">
-        <v>80603</v>
+        <v>80607</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>136996263</v>
       </c>
       <c r="B122" t="n">
-        <v>80603</v>
+        <v>80607</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>136996264</v>
       </c>
       <c r="B123" t="n">
-        <v>80603</v>
+        <v>80607</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>136996265</v>
       </c>
       <c r="B124" t="n">
-        <v>80603</v>
+        <v>80607</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -17195,7 +17195,7 @@
         <v>136996266</v>
       </c>
       <c r="B125" t="n">
-        <v>80603</v>
+        <v>80607</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -17330,7 +17330,7 @@
         <v>136996267</v>
       </c>
       <c r="B126" t="n">
-        <v>80603</v>
+        <v>80607</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -17465,7 +17465,7 @@
         <v>136996268</v>
       </c>
       <c r="B127" t="n">
-        <v>80603</v>
+        <v>80607</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>136996269</v>
       </c>
       <c r="B144" t="n">
-        <v>111332</v>
+        <v>111338</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
         <v>136996270</v>
       </c>
       <c r="B145" t="n">
-        <v>111332</v>
+        <v>111338</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>136996271</v>
       </c>
       <c r="B146" t="n">
-        <v>111332</v>
+        <v>111338</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>136996274</v>
       </c>
       <c r="B147" t="n">
-        <v>111332</v>
+        <v>111338</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>136996275</v>
       </c>
       <c r="B148" t="n">
-        <v>111332</v>
+        <v>111338</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>136996278</v>
       </c>
       <c r="B150" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>136996279</v>
       </c>
       <c r="B151" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -20695,7 +20695,7 @@
         <v>136996282</v>
       </c>
       <c r="B152" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>136996283</v>
       </c>
       <c r="B153" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -20953,7 +20953,7 @@
         <v>136996221</v>
       </c>
       <c r="B154" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>

--- a/artfynd/A 17248-2026 artfynd.xlsx
+++ b/artfynd/A 17248-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136996334</v>
       </c>
       <c r="B2" t="n">
-        <v>89476</v>
+        <v>89478</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>136996333</v>
       </c>
       <c r="B3" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>136996220</v>
       </c>
       <c r="B4" t="n">
-        <v>80596</v>
+        <v>80598</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>136996284</v>
       </c>
       <c r="B22" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>136996285</v>
       </c>
       <c r="B23" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>136996286</v>
       </c>
       <c r="B24" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>136996287</v>
       </c>
       <c r="B25" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>136996288</v>
       </c>
       <c r="B26" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>136996289</v>
       </c>
       <c r="B27" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>136996290</v>
       </c>
       <c r="B28" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>136996292</v>
       </c>
       <c r="B29" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>136996293</v>
       </c>
       <c r="B30" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         <v>136996294</v>
       </c>
       <c r="B31" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>136996295</v>
       </c>
       <c r="B32" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>136996297</v>
       </c>
       <c r="B33" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4913,7 +4913,7 @@
         <v>136996298</v>
       </c>
       <c r="B34" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
         <v>136996299</v>
       </c>
       <c r="B35" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>136996300</v>
       </c>
       <c r="B36" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>136996301</v>
       </c>
       <c r="B37" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>136996302</v>
       </c>
       <c r="B38" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>136996303</v>
       </c>
       <c r="B39" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>136996304</v>
       </c>
       <c r="B40" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>136996305</v>
       </c>
       <c r="B41" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>136996306</v>
       </c>
       <c r="B42" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>136996307</v>
       </c>
       <c r="B43" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>136996308</v>
       </c>
       <c r="B44" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>136996309</v>
       </c>
       <c r="B45" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>136996310</v>
       </c>
       <c r="B46" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>136996311</v>
       </c>
       <c r="B47" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>136996313</v>
       </c>
       <c r="B48" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>136996314</v>
       </c>
       <c r="B49" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>136996315</v>
       </c>
       <c r="B50" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>136996316</v>
       </c>
       <c r="B51" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>136996317</v>
       </c>
       <c r="B52" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>136996318</v>
       </c>
       <c r="B53" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>136996319</v>
       </c>
       <c r="B54" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>136996320</v>
       </c>
       <c r="B55" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>136996321</v>
       </c>
       <c r="B56" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>136996322</v>
       </c>
       <c r="B57" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>136996323</v>
       </c>
       <c r="B58" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>136996324</v>
       </c>
       <c r="B59" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>136996325</v>
       </c>
       <c r="B60" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>136996326</v>
       </c>
       <c r="B61" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>136996332</v>
       </c>
       <c r="B62" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>136996223</v>
       </c>
       <c r="B65" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>136996224</v>
       </c>
       <c r="B66" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>136996225</v>
       </c>
       <c r="B67" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>136996226</v>
       </c>
       <c r="B68" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>136996228</v>
       </c>
       <c r="B69" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>136996229</v>
       </c>
       <c r="B70" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9891,7 +9891,7 @@
         <v>136996230</v>
       </c>
       <c r="B71" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>136996231</v>
       </c>
       <c r="B72" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>136996232</v>
       </c>
       <c r="B73" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>136996233</v>
       </c>
       <c r="B74" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>136996234</v>
       </c>
       <c r="B75" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>136996235</v>
       </c>
       <c r="B76" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>136996236</v>
       </c>
       <c r="B77" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>136996237</v>
       </c>
       <c r="B78" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10969,7 +10969,7 @@
         <v>136996239</v>
       </c>
       <c r="B79" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -11100,7 +11100,7 @@
         <v>136996240</v>
       </c>
       <c r="B80" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11235,7 +11235,7 @@
         <v>136996241</v>
       </c>
       <c r="B81" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -11371,7 +11371,7 @@
         <v>136996242</v>
       </c>
       <c r="B82" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>136996243</v>
       </c>
       <c r="B83" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11646,7 +11646,7 @@
         <v>136996244</v>
       </c>
       <c r="B84" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>136996245</v>
       </c>
       <c r="B85" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         <v>136996246</v>
       </c>
       <c r="B86" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>136996247</v>
       </c>
       <c r="B87" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         <v>136996248</v>
       </c>
       <c r="B88" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         <v>136996249</v>
       </c>
       <c r="B89" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>136996204</v>
       </c>
       <c r="B94" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -13114,7 +13114,7 @@
         <v>136996205</v>
       </c>
       <c r="B95" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -13249,7 +13249,7 @@
         <v>136996207</v>
       </c>
       <c r="B96" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>136996208</v>
       </c>
       <c r="B97" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
         <v>136996209</v>
       </c>
       <c r="B98" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>136996210</v>
       </c>
       <c r="B99" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13789,7 +13789,7 @@
         <v>136996211</v>
       </c>
       <c r="B100" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>136996212</v>
       </c>
       <c r="B101" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>136996213</v>
       </c>
       <c r="B102" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>136996214</v>
       </c>
       <c r="B103" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -14329,7 +14329,7 @@
         <v>136996215</v>
       </c>
       <c r="B104" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -14464,7 +14464,7 @@
         <v>136996216</v>
       </c>
       <c r="B105" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -14599,7 +14599,7 @@
         <v>136996218</v>
       </c>
       <c r="B106" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14734,7 +14734,7 @@
         <v>136996335</v>
       </c>
       <c r="B107" t="n">
-        <v>80606</v>
+        <v>80608</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>136996250</v>
       </c>
       <c r="B109" t="n">
-        <v>80607</v>
+        <v>80609</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>136996251</v>
       </c>
       <c r="B110" t="n">
-        <v>80607</v>
+        <v>80609</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>136996252</v>
       </c>
       <c r="B111" t="n">
-        <v>80607</v>
+        <v>80609</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         <v>136996253</v>
       </c>
       <c r="B112" t="n">
-        <v>80607</v>
+        <v>80609</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>136996254</v>
       </c>
       <c r="B113" t="n">
-        <v>80607</v>
+        <v>80609</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
         <v>136996255</v>
       </c>
       <c r="B114" t="n">
-        <v>80607</v>
+        <v>80609</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -15825,7 +15825,7 @@
         <v>136996256</v>
       </c>
       <c r="B115" t="n">
-        <v>80607</v>
+        <v>80609</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>136996257</v>
       </c>
       <c r="B116" t="n">
-        <v>80607</v>
+        <v>80609</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>136996258</v>
       </c>
       <c r="B117" t="n">
-        <v>80607</v>
+        <v>80609</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>136996259</v>
       </c>
       <c r="B118" t="n">
-        <v>80607</v>
+        <v>80609</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>136996260</v>
       </c>
       <c r="B119" t="n">
-        <v>80607</v>
+        <v>80609</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>136996261</v>
       </c>
       <c r="B120" t="n">
-        <v>80607</v>
+        <v>80609</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>136996262</v>
       </c>
       <c r="B121" t="n">
-        <v>80607</v>
+        <v>80609</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>136996263</v>
       </c>
       <c r="B122" t="n">
-        <v>80607</v>
+        <v>80609</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>136996264</v>
       </c>
       <c r="B123" t="n">
-        <v>80607</v>
+        <v>80609</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>136996265</v>
       </c>
       <c r="B124" t="n">
-        <v>80607</v>
+        <v>80609</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -17195,7 +17195,7 @@
         <v>136996266</v>
       </c>
       <c r="B125" t="n">
-        <v>80607</v>
+        <v>80609</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -17330,7 +17330,7 @@
         <v>136996267</v>
       </c>
       <c r="B126" t="n">
-        <v>80607</v>
+        <v>80609</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -17465,7 +17465,7 @@
         <v>136996268</v>
       </c>
       <c r="B127" t="n">
-        <v>80607</v>
+        <v>80609</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>136996269</v>
       </c>
       <c r="B144" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
         <v>136996270</v>
       </c>
       <c r="B145" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>136996271</v>
       </c>
       <c r="B146" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>136996274</v>
       </c>
       <c r="B147" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>136996275</v>
       </c>
       <c r="B148" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>136996278</v>
       </c>
       <c r="B150" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>136996279</v>
       </c>
       <c r="B151" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -20695,7 +20695,7 @@
         <v>136996282</v>
       </c>
       <c r="B152" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>136996283</v>
       </c>
       <c r="B153" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -20953,7 +20953,7 @@
         <v>136996221</v>
       </c>
       <c r="B154" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>

--- a/artfynd/A 17248-2026 artfynd.xlsx
+++ b/artfynd/A 17248-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136996334</v>
       </c>
       <c r="B2" t="n">
-        <v>89478</v>
+        <v>89479</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>136996333</v>
       </c>
       <c r="B3" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>136996220</v>
       </c>
       <c r="B4" t="n">
-        <v>80598</v>
+        <v>80599</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>136996284</v>
       </c>
       <c r="B22" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>136996285</v>
       </c>
       <c r="B23" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>136996286</v>
       </c>
       <c r="B24" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>136996287</v>
       </c>
       <c r="B25" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>136996288</v>
       </c>
       <c r="B26" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>136996289</v>
       </c>
       <c r="B27" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>136996290</v>
       </c>
       <c r="B28" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>136996292</v>
       </c>
       <c r="B29" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>136996293</v>
       </c>
       <c r="B30" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         <v>136996294</v>
       </c>
       <c r="B31" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>136996295</v>
       </c>
       <c r="B32" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>136996297</v>
       </c>
       <c r="B33" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4913,7 +4913,7 @@
         <v>136996298</v>
       </c>
       <c r="B34" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
         <v>136996299</v>
       </c>
       <c r="B35" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>136996300</v>
       </c>
       <c r="B36" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>136996301</v>
       </c>
       <c r="B37" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>136996302</v>
       </c>
       <c r="B38" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>136996303</v>
       </c>
       <c r="B39" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>136996304</v>
       </c>
       <c r="B40" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>136996305</v>
       </c>
       <c r="B41" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>136996306</v>
       </c>
       <c r="B42" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>136996307</v>
       </c>
       <c r="B43" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>136996308</v>
       </c>
       <c r="B44" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>136996309</v>
       </c>
       <c r="B45" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>136996310</v>
       </c>
       <c r="B46" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>136996311</v>
       </c>
       <c r="B47" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>136996313</v>
       </c>
       <c r="B48" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>136996314</v>
       </c>
       <c r="B49" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>136996315</v>
       </c>
       <c r="B50" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>136996316</v>
       </c>
       <c r="B51" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>136996317</v>
       </c>
       <c r="B52" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>136996318</v>
       </c>
       <c r="B53" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>136996319</v>
       </c>
       <c r="B54" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>136996320</v>
       </c>
       <c r="B55" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>136996321</v>
       </c>
       <c r="B56" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>136996322</v>
       </c>
       <c r="B57" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>136996323</v>
       </c>
       <c r="B58" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>136996324</v>
       </c>
       <c r="B59" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>136996325</v>
       </c>
       <c r="B60" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>136996326</v>
       </c>
       <c r="B61" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>136996332</v>
       </c>
       <c r="B62" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>136996223</v>
       </c>
       <c r="B65" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>136996224</v>
       </c>
       <c r="B66" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>136996225</v>
       </c>
       <c r="B67" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>136996226</v>
       </c>
       <c r="B68" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>136996228</v>
       </c>
       <c r="B69" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>136996229</v>
       </c>
       <c r="B70" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9891,7 +9891,7 @@
         <v>136996230</v>
       </c>
       <c r="B71" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>136996231</v>
       </c>
       <c r="B72" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>136996232</v>
       </c>
       <c r="B73" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>136996233</v>
       </c>
       <c r="B74" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>136996234</v>
       </c>
       <c r="B75" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>136996235</v>
       </c>
       <c r="B76" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>136996236</v>
       </c>
       <c r="B77" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>136996237</v>
       </c>
       <c r="B78" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10969,7 +10969,7 @@
         <v>136996239</v>
       </c>
       <c r="B79" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -11100,7 +11100,7 @@
         <v>136996240</v>
       </c>
       <c r="B80" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11235,7 +11235,7 @@
         <v>136996241</v>
       </c>
       <c r="B81" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -11371,7 +11371,7 @@
         <v>136996242</v>
       </c>
       <c r="B82" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>136996243</v>
       </c>
       <c r="B83" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11646,7 +11646,7 @@
         <v>136996244</v>
       </c>
       <c r="B84" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>136996245</v>
       </c>
       <c r="B85" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         <v>136996246</v>
       </c>
       <c r="B86" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>136996247</v>
       </c>
       <c r="B87" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         <v>136996248</v>
       </c>
       <c r="B88" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         <v>136996249</v>
       </c>
       <c r="B89" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>136996204</v>
       </c>
       <c r="B94" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -13114,7 +13114,7 @@
         <v>136996205</v>
       </c>
       <c r="B95" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -13249,7 +13249,7 @@
         <v>136996207</v>
       </c>
       <c r="B96" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>136996208</v>
       </c>
       <c r="B97" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
         <v>136996209</v>
       </c>
       <c r="B98" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>136996210</v>
       </c>
       <c r="B99" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13789,7 +13789,7 @@
         <v>136996211</v>
       </c>
       <c r="B100" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>136996212</v>
       </c>
       <c r="B101" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>136996213</v>
       </c>
       <c r="B102" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>136996214</v>
       </c>
       <c r="B103" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -14329,7 +14329,7 @@
         <v>136996215</v>
       </c>
       <c r="B104" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -14464,7 +14464,7 @@
         <v>136996216</v>
       </c>
       <c r="B105" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -14599,7 +14599,7 @@
         <v>136996218</v>
       </c>
       <c r="B106" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14734,7 +14734,7 @@
         <v>136996335</v>
       </c>
       <c r="B107" t="n">
-        <v>80608</v>
+        <v>80609</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>136996250</v>
       </c>
       <c r="B109" t="n">
-        <v>80609</v>
+        <v>80610</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>136996251</v>
       </c>
       <c r="B110" t="n">
-        <v>80609</v>
+        <v>80610</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>136996252</v>
       </c>
       <c r="B111" t="n">
-        <v>80609</v>
+        <v>80610</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         <v>136996253</v>
       </c>
       <c r="B112" t="n">
-        <v>80609</v>
+        <v>80610</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>136996254</v>
       </c>
       <c r="B113" t="n">
-        <v>80609</v>
+        <v>80610</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
         <v>136996255</v>
       </c>
       <c r="B114" t="n">
-        <v>80609</v>
+        <v>80610</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -15825,7 +15825,7 @@
         <v>136996256</v>
       </c>
       <c r="B115" t="n">
-        <v>80609</v>
+        <v>80610</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>136996257</v>
       </c>
       <c r="B116" t="n">
-        <v>80609</v>
+        <v>80610</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>136996258</v>
       </c>
       <c r="B117" t="n">
-        <v>80609</v>
+        <v>80610</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>136996259</v>
       </c>
       <c r="B118" t="n">
-        <v>80609</v>
+        <v>80610</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>136996260</v>
       </c>
       <c r="B119" t="n">
-        <v>80609</v>
+        <v>80610</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>136996261</v>
       </c>
       <c r="B120" t="n">
-        <v>80609</v>
+        <v>80610</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>136996262</v>
       </c>
       <c r="B121" t="n">
-        <v>80609</v>
+        <v>80610</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>136996263</v>
       </c>
       <c r="B122" t="n">
-        <v>80609</v>
+        <v>80610</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>136996264</v>
       </c>
       <c r="B123" t="n">
-        <v>80609</v>
+        <v>80610</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>136996265</v>
       </c>
       <c r="B124" t="n">
-        <v>80609</v>
+        <v>80610</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -17195,7 +17195,7 @@
         <v>136996266</v>
       </c>
       <c r="B125" t="n">
-        <v>80609</v>
+        <v>80610</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -17330,7 +17330,7 @@
         <v>136996267</v>
       </c>
       <c r="B126" t="n">
-        <v>80609</v>
+        <v>80610</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -17465,7 +17465,7 @@
         <v>136996268</v>
       </c>
       <c r="B127" t="n">
-        <v>80609</v>
+        <v>80610</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>136996269</v>
       </c>
       <c r="B144" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
         <v>136996270</v>
       </c>
       <c r="B145" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>136996271</v>
       </c>
       <c r="B146" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>136996274</v>
       </c>
       <c r="B147" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>136996275</v>
       </c>
       <c r="B148" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>136996278</v>
       </c>
       <c r="B150" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>136996279</v>
       </c>
       <c r="B151" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -20695,7 +20695,7 @@
         <v>136996282</v>
       </c>
       <c r="B152" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>136996283</v>
       </c>
       <c r="B153" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -20953,7 +20953,7 @@
         <v>136996221</v>
       </c>
       <c r="B154" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>

--- a/artfynd/A 17248-2026 artfynd.xlsx
+++ b/artfynd/A 17248-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136996334</v>
       </c>
       <c r="B2" t="n">
-        <v>89479</v>
+        <v>89485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>136996269</v>
       </c>
       <c r="B144" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
         <v>136996270</v>
       </c>
       <c r="B145" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>136996271</v>
       </c>
       <c r="B146" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>136996274</v>
       </c>
       <c r="B147" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>136996275</v>
       </c>
       <c r="B148" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>136996278</v>
       </c>
       <c r="B150" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>136996279</v>
       </c>
       <c r="B151" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -20695,7 +20695,7 @@
         <v>136996282</v>
       </c>
       <c r="B152" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>136996283</v>
       </c>
       <c r="B153" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -20953,7 +20953,7 @@
         <v>136996221</v>
       </c>
       <c r="B154" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>

--- a/artfynd/A 17248-2026 artfynd.xlsx
+++ b/artfynd/A 17248-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136996334</v>
       </c>
       <c r="B2" t="n">
-        <v>89485</v>
+        <v>89489</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>136996333</v>
       </c>
       <c r="B3" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>136996220</v>
       </c>
       <c r="B4" t="n">
-        <v>80599</v>
+        <v>80601</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>136996284</v>
       </c>
       <c r="B22" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>136996285</v>
       </c>
       <c r="B23" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>136996286</v>
       </c>
       <c r="B24" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>136996287</v>
       </c>
       <c r="B25" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>136996288</v>
       </c>
       <c r="B26" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>136996289</v>
       </c>
       <c r="B27" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>136996290</v>
       </c>
       <c r="B28" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>136996292</v>
       </c>
       <c r="B29" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>136996293</v>
       </c>
       <c r="B30" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         <v>136996294</v>
       </c>
       <c r="B31" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>136996295</v>
       </c>
       <c r="B32" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>136996297</v>
       </c>
       <c r="B33" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4913,7 +4913,7 @@
         <v>136996298</v>
       </c>
       <c r="B34" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
         <v>136996299</v>
       </c>
       <c r="B35" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>136996300</v>
       </c>
       <c r="B36" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>136996301</v>
       </c>
       <c r="B37" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>136996302</v>
       </c>
       <c r="B38" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>136996303</v>
       </c>
       <c r="B39" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>136996304</v>
       </c>
       <c r="B40" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>136996305</v>
       </c>
       <c r="B41" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>136996306</v>
       </c>
       <c r="B42" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>136996307</v>
       </c>
       <c r="B43" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>136996308</v>
       </c>
       <c r="B44" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>136996309</v>
       </c>
       <c r="B45" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>136996310</v>
       </c>
       <c r="B46" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>136996311</v>
       </c>
       <c r="B47" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>136996313</v>
       </c>
       <c r="B48" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>136996314</v>
       </c>
       <c r="B49" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>136996315</v>
       </c>
       <c r="B50" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>136996316</v>
       </c>
       <c r="B51" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>136996317</v>
       </c>
       <c r="B52" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>136996318</v>
       </c>
       <c r="B53" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>136996319</v>
       </c>
       <c r="B54" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>136996320</v>
       </c>
       <c r="B55" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>136996321</v>
       </c>
       <c r="B56" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>136996322</v>
       </c>
       <c r="B57" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>136996323</v>
       </c>
       <c r="B58" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>136996324</v>
       </c>
       <c r="B59" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>136996325</v>
       </c>
       <c r="B60" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>136996326</v>
       </c>
       <c r="B61" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>136996332</v>
       </c>
       <c r="B62" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>136996223</v>
       </c>
       <c r="B65" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>136996224</v>
       </c>
       <c r="B66" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>136996225</v>
       </c>
       <c r="B67" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>136996226</v>
       </c>
       <c r="B68" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>136996228</v>
       </c>
       <c r="B69" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>136996229</v>
       </c>
       <c r="B70" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9891,7 +9891,7 @@
         <v>136996230</v>
       </c>
       <c r="B71" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>136996231</v>
       </c>
       <c r="B72" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>136996232</v>
       </c>
       <c r="B73" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>136996233</v>
       </c>
       <c r="B74" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>136996234</v>
       </c>
       <c r="B75" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>136996235</v>
       </c>
       <c r="B76" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>136996236</v>
       </c>
       <c r="B77" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>136996237</v>
       </c>
       <c r="B78" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10969,7 +10969,7 @@
         <v>136996239</v>
       </c>
       <c r="B79" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -11100,7 +11100,7 @@
         <v>136996240</v>
       </c>
       <c r="B80" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11235,7 +11235,7 @@
         <v>136996241</v>
       </c>
       <c r="B81" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -11371,7 +11371,7 @@
         <v>136996242</v>
       </c>
       <c r="B82" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>136996243</v>
       </c>
       <c r="B83" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11646,7 +11646,7 @@
         <v>136996244</v>
       </c>
       <c r="B84" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>136996245</v>
       </c>
       <c r="B85" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         <v>136996246</v>
       </c>
       <c r="B86" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>136996247</v>
       </c>
       <c r="B87" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         <v>136996248</v>
       </c>
       <c r="B88" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         <v>136996249</v>
       </c>
       <c r="B89" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>136996204</v>
       </c>
       <c r="B94" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -13114,7 +13114,7 @@
         <v>136996205</v>
       </c>
       <c r="B95" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -13249,7 +13249,7 @@
         <v>136996207</v>
       </c>
       <c r="B96" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>136996208</v>
       </c>
       <c r="B97" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
         <v>136996209</v>
       </c>
       <c r="B98" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>136996210</v>
       </c>
       <c r="B99" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13789,7 +13789,7 @@
         <v>136996211</v>
       </c>
       <c r="B100" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>136996212</v>
       </c>
       <c r="B101" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>136996213</v>
       </c>
       <c r="B102" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>136996214</v>
       </c>
       <c r="B103" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -14329,7 +14329,7 @@
         <v>136996215</v>
       </c>
       <c r="B104" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -14464,7 +14464,7 @@
         <v>136996216</v>
       </c>
       <c r="B105" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -14599,7 +14599,7 @@
         <v>136996218</v>
       </c>
       <c r="B106" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14734,7 +14734,7 @@
         <v>136996335</v>
       </c>
       <c r="B107" t="n">
-        <v>80609</v>
+        <v>80611</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>136996250</v>
       </c>
       <c r="B109" t="n">
-        <v>80610</v>
+        <v>80612</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>136996251</v>
       </c>
       <c r="B110" t="n">
-        <v>80610</v>
+        <v>80612</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>136996252</v>
       </c>
       <c r="B111" t="n">
-        <v>80610</v>
+        <v>80612</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         <v>136996253</v>
       </c>
       <c r="B112" t="n">
-        <v>80610</v>
+        <v>80612</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>136996254</v>
       </c>
       <c r="B113" t="n">
-        <v>80610</v>
+        <v>80612</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
         <v>136996255</v>
       </c>
       <c r="B114" t="n">
-        <v>80610</v>
+        <v>80612</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -15825,7 +15825,7 @@
         <v>136996256</v>
       </c>
       <c r="B115" t="n">
-        <v>80610</v>
+        <v>80612</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>136996257</v>
       </c>
       <c r="B116" t="n">
-        <v>80610</v>
+        <v>80612</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>136996258</v>
       </c>
       <c r="B117" t="n">
-        <v>80610</v>
+        <v>80612</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>136996259</v>
       </c>
       <c r="B118" t="n">
-        <v>80610</v>
+        <v>80612</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>136996260</v>
       </c>
       <c r="B119" t="n">
-        <v>80610</v>
+        <v>80612</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>136996261</v>
       </c>
       <c r="B120" t="n">
-        <v>80610</v>
+        <v>80612</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>136996262</v>
       </c>
       <c r="B121" t="n">
-        <v>80610</v>
+        <v>80612</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>136996263</v>
       </c>
       <c r="B122" t="n">
-        <v>80610</v>
+        <v>80612</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>136996264</v>
       </c>
       <c r="B123" t="n">
-        <v>80610</v>
+        <v>80612</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>136996265</v>
       </c>
       <c r="B124" t="n">
-        <v>80610</v>
+        <v>80612</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -17195,7 +17195,7 @@
         <v>136996266</v>
       </c>
       <c r="B125" t="n">
-        <v>80610</v>
+        <v>80612</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -17330,7 +17330,7 @@
         <v>136996267</v>
       </c>
       <c r="B126" t="n">
-        <v>80610</v>
+        <v>80612</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -17465,7 +17465,7 @@
         <v>136996268</v>
       </c>
       <c r="B127" t="n">
-        <v>80610</v>
+        <v>80612</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>136996269</v>
       </c>
       <c r="B144" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
         <v>136996270</v>
       </c>
       <c r="B145" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>136996271</v>
       </c>
       <c r="B146" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>136996274</v>
       </c>
       <c r="B147" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>136996275</v>
       </c>
       <c r="B148" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>136996278</v>
       </c>
       <c r="B150" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>136996279</v>
       </c>
       <c r="B151" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -20695,7 +20695,7 @@
         <v>136996282</v>
       </c>
       <c r="B152" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>136996283</v>
       </c>
       <c r="B153" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -20953,7 +20953,7 @@
         <v>136996221</v>
       </c>
       <c r="B154" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>

--- a/artfynd/A 17248-2026 artfynd.xlsx
+++ b/artfynd/A 17248-2026 artfynd.xlsx
@@ -19724,7 +19724,7 @@
         <v>136996269</v>
       </c>
       <c r="B144" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
         <v>136996270</v>
       </c>
       <c r="B145" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>136996271</v>
       </c>
       <c r="B146" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>136996274</v>
       </c>
       <c r="B147" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>136996275</v>
       </c>
       <c r="B148" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>136996278</v>
       </c>
       <c r="B150" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>136996279</v>
       </c>
       <c r="B151" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -20695,7 +20695,7 @@
         <v>136996282</v>
       </c>
       <c r="B152" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>136996283</v>
       </c>
       <c r="B153" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -20953,7 +20953,7 @@
         <v>136996221</v>
       </c>
       <c r="B154" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>

--- a/artfynd/A 17248-2026 artfynd.xlsx
+++ b/artfynd/A 17248-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136996334</v>
       </c>
       <c r="B2" t="n">
-        <v>89489</v>
+        <v>89491</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>136996333</v>
       </c>
       <c r="B3" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>136996220</v>
       </c>
       <c r="B4" t="n">
-        <v>80601</v>
+        <v>80604</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>136996284</v>
       </c>
       <c r="B22" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>136996285</v>
       </c>
       <c r="B23" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>136996286</v>
       </c>
       <c r="B24" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>136996287</v>
       </c>
       <c r="B25" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>136996288</v>
       </c>
       <c r="B26" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>136996289</v>
       </c>
       <c r="B27" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>136996290</v>
       </c>
       <c r="B28" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>136996292</v>
       </c>
       <c r="B29" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>136996293</v>
       </c>
       <c r="B30" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         <v>136996294</v>
       </c>
       <c r="B31" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>136996295</v>
       </c>
       <c r="B32" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>136996297</v>
       </c>
       <c r="B33" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4913,7 +4913,7 @@
         <v>136996298</v>
       </c>
       <c r="B34" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
         <v>136996299</v>
       </c>
       <c r="B35" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>136996300</v>
       </c>
       <c r="B36" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>136996301</v>
       </c>
       <c r="B37" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>136996302</v>
       </c>
       <c r="B38" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>136996303</v>
       </c>
       <c r="B39" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>136996304</v>
       </c>
       <c r="B40" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>136996305</v>
       </c>
       <c r="B41" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>136996306</v>
       </c>
       <c r="B42" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>136996307</v>
       </c>
       <c r="B43" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>136996308</v>
       </c>
       <c r="B44" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>136996309</v>
       </c>
       <c r="B45" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>136996310</v>
       </c>
       <c r="B46" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>136996311</v>
       </c>
       <c r="B47" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>136996313</v>
       </c>
       <c r="B48" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>136996314</v>
       </c>
       <c r="B49" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>136996315</v>
       </c>
       <c r="B50" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>136996316</v>
       </c>
       <c r="B51" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>136996317</v>
       </c>
       <c r="B52" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>136996318</v>
       </c>
       <c r="B53" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>136996319</v>
       </c>
       <c r="B54" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>136996320</v>
       </c>
       <c r="B55" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>136996321</v>
       </c>
       <c r="B56" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>136996322</v>
       </c>
       <c r="B57" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>136996323</v>
       </c>
       <c r="B58" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>136996324</v>
       </c>
       <c r="B59" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>136996325</v>
       </c>
       <c r="B60" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>136996326</v>
       </c>
       <c r="B61" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>136996332</v>
       </c>
       <c r="B62" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>136996223</v>
       </c>
       <c r="B65" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>136996224</v>
       </c>
       <c r="B66" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>136996225</v>
       </c>
       <c r="B67" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>136996226</v>
       </c>
       <c r="B68" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>136996228</v>
       </c>
       <c r="B69" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>136996229</v>
       </c>
       <c r="B70" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9891,7 +9891,7 @@
         <v>136996230</v>
       </c>
       <c r="B71" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>136996231</v>
       </c>
       <c r="B72" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>136996232</v>
       </c>
       <c r="B73" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>136996233</v>
       </c>
       <c r="B74" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>136996234</v>
       </c>
       <c r="B75" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>136996235</v>
       </c>
       <c r="B76" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>136996236</v>
       </c>
       <c r="B77" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>136996237</v>
       </c>
       <c r="B78" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10969,7 +10969,7 @@
         <v>136996239</v>
       </c>
       <c r="B79" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -11100,7 +11100,7 @@
         <v>136996240</v>
       </c>
       <c r="B80" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11235,7 +11235,7 @@
         <v>136996241</v>
       </c>
       <c r="B81" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -11371,7 +11371,7 @@
         <v>136996242</v>
       </c>
       <c r="B82" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>136996243</v>
       </c>
       <c r="B83" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11646,7 +11646,7 @@
         <v>136996244</v>
       </c>
       <c r="B84" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>136996245</v>
       </c>
       <c r="B85" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         <v>136996246</v>
       </c>
       <c r="B86" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>136996247</v>
       </c>
       <c r="B87" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         <v>136996248</v>
       </c>
       <c r="B88" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         <v>136996249</v>
       </c>
       <c r="B89" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>136996204</v>
       </c>
       <c r="B94" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -13114,7 +13114,7 @@
         <v>136996205</v>
       </c>
       <c r="B95" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -13249,7 +13249,7 @@
         <v>136996207</v>
       </c>
       <c r="B96" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>136996208</v>
       </c>
       <c r="B97" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
         <v>136996209</v>
       </c>
       <c r="B98" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>136996210</v>
       </c>
       <c r="B99" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13789,7 +13789,7 @@
         <v>136996211</v>
       </c>
       <c r="B100" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>136996212</v>
       </c>
       <c r="B101" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>136996213</v>
       </c>
       <c r="B102" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>136996214</v>
       </c>
       <c r="B103" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -14329,7 +14329,7 @@
         <v>136996215</v>
       </c>
       <c r="B104" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -14464,7 +14464,7 @@
         <v>136996216</v>
       </c>
       <c r="B105" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -14599,7 +14599,7 @@
         <v>136996218</v>
       </c>
       <c r="B106" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14734,7 +14734,7 @@
         <v>136996335</v>
       </c>
       <c r="B107" t="n">
-        <v>80611</v>
+        <v>80614</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>136996250</v>
       </c>
       <c r="B109" t="n">
-        <v>80612</v>
+        <v>80615</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>136996251</v>
       </c>
       <c r="B110" t="n">
-        <v>80612</v>
+        <v>80615</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>136996252</v>
       </c>
       <c r="B111" t="n">
-        <v>80612</v>
+        <v>80615</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         <v>136996253</v>
       </c>
       <c r="B112" t="n">
-        <v>80612</v>
+        <v>80615</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>136996254</v>
       </c>
       <c r="B113" t="n">
-        <v>80612</v>
+        <v>80615</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
         <v>136996255</v>
       </c>
       <c r="B114" t="n">
-        <v>80612</v>
+        <v>80615</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -15825,7 +15825,7 @@
         <v>136996256</v>
       </c>
       <c r="B115" t="n">
-        <v>80612</v>
+        <v>80615</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>136996257</v>
       </c>
       <c r="B116" t="n">
-        <v>80612</v>
+        <v>80615</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>136996258</v>
       </c>
       <c r="B117" t="n">
-        <v>80612</v>
+        <v>80615</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>136996259</v>
       </c>
       <c r="B118" t="n">
-        <v>80612</v>
+        <v>80615</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>136996260</v>
       </c>
       <c r="B119" t="n">
-        <v>80612</v>
+        <v>80615</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>136996261</v>
       </c>
       <c r="B120" t="n">
-        <v>80612</v>
+        <v>80615</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>136996262</v>
       </c>
       <c r="B121" t="n">
-        <v>80612</v>
+        <v>80615</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>136996263</v>
       </c>
       <c r="B122" t="n">
-        <v>80612</v>
+        <v>80615</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>136996264</v>
       </c>
       <c r="B123" t="n">
-        <v>80612</v>
+        <v>80615</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>136996265</v>
       </c>
       <c r="B124" t="n">
-        <v>80612</v>
+        <v>80615</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -17195,7 +17195,7 @@
         <v>136996266</v>
       </c>
       <c r="B125" t="n">
-        <v>80612</v>
+        <v>80615</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -17330,7 +17330,7 @@
         <v>136996267</v>
       </c>
       <c r="B126" t="n">
-        <v>80612</v>
+        <v>80615</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -17465,7 +17465,7 @@
         <v>136996268</v>
       </c>
       <c r="B127" t="n">
-        <v>80612</v>
+        <v>80615</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>136996269</v>
       </c>
       <c r="B144" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
         <v>136996270</v>
       </c>
       <c r="B145" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>136996271</v>
       </c>
       <c r="B146" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>136996274</v>
       </c>
       <c r="B147" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>136996275</v>
       </c>
       <c r="B148" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>136996278</v>
       </c>
       <c r="B150" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>136996279</v>
       </c>
       <c r="B151" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -20695,7 +20695,7 @@
         <v>136996282</v>
       </c>
       <c r="B152" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>136996283</v>
       </c>
       <c r="B153" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -20953,7 +20953,7 @@
         <v>136996221</v>
       </c>
       <c r="B154" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>

--- a/artfynd/A 17248-2026 artfynd.xlsx
+++ b/artfynd/A 17248-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136996334</v>
       </c>
       <c r="B2" t="n">
-        <v>89491</v>
+        <v>89504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>136996333</v>
       </c>
       <c r="B3" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>136996220</v>
       </c>
       <c r="B4" t="n">
-        <v>80604</v>
+        <v>80617</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>136996284</v>
       </c>
       <c r="B22" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>136996285</v>
       </c>
       <c r="B23" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>136996286</v>
       </c>
       <c r="B24" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>136996287</v>
       </c>
       <c r="B25" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>136996288</v>
       </c>
       <c r="B26" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>136996289</v>
       </c>
       <c r="B27" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>136996290</v>
       </c>
       <c r="B28" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>136996292</v>
       </c>
       <c r="B29" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>136996293</v>
       </c>
       <c r="B30" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         <v>136996294</v>
       </c>
       <c r="B31" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>136996295</v>
       </c>
       <c r="B32" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>136996297</v>
       </c>
       <c r="B33" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4913,7 +4913,7 @@
         <v>136996298</v>
       </c>
       <c r="B34" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
         <v>136996299</v>
       </c>
       <c r="B35" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>136996300</v>
       </c>
       <c r="B36" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>136996301</v>
       </c>
       <c r="B37" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>136996302</v>
       </c>
       <c r="B38" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>136996303</v>
       </c>
       <c r="B39" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>136996304</v>
       </c>
       <c r="B40" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>136996305</v>
       </c>
       <c r="B41" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>136996306</v>
       </c>
       <c r="B42" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>136996307</v>
       </c>
       <c r="B43" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>136996308</v>
       </c>
       <c r="B44" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>136996309</v>
       </c>
       <c r="B45" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>136996310</v>
       </c>
       <c r="B46" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>136996311</v>
       </c>
       <c r="B47" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>136996313</v>
       </c>
       <c r="B48" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>136996314</v>
       </c>
       <c r="B49" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>136996315</v>
       </c>
       <c r="B50" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>136996316</v>
       </c>
       <c r="B51" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>136996317</v>
       </c>
       <c r="B52" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>136996318</v>
       </c>
       <c r="B53" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>136996319</v>
       </c>
       <c r="B54" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>136996320</v>
       </c>
       <c r="B55" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>136996321</v>
       </c>
       <c r="B56" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>136996322</v>
       </c>
       <c r="B57" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>136996323</v>
       </c>
       <c r="B58" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>136996324</v>
       </c>
       <c r="B59" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>136996325</v>
       </c>
       <c r="B60" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>136996326</v>
       </c>
       <c r="B61" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>136996332</v>
       </c>
       <c r="B62" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>136996223</v>
       </c>
       <c r="B65" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>136996224</v>
       </c>
       <c r="B66" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>136996225</v>
       </c>
       <c r="B67" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>136996226</v>
       </c>
       <c r="B68" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>136996228</v>
       </c>
       <c r="B69" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>136996229</v>
       </c>
       <c r="B70" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9891,7 +9891,7 @@
         <v>136996230</v>
       </c>
       <c r="B71" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>136996231</v>
       </c>
       <c r="B72" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>136996232</v>
       </c>
       <c r="B73" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>136996233</v>
       </c>
       <c r="B74" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>136996234</v>
       </c>
       <c r="B75" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>136996235</v>
       </c>
       <c r="B76" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>136996236</v>
       </c>
       <c r="B77" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>136996237</v>
       </c>
       <c r="B78" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10969,7 +10969,7 @@
         <v>136996239</v>
       </c>
       <c r="B79" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -11100,7 +11100,7 @@
         <v>136996240</v>
       </c>
       <c r="B80" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11235,7 +11235,7 @@
         <v>136996241</v>
       </c>
       <c r="B81" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -11371,7 +11371,7 @@
         <v>136996242</v>
       </c>
       <c r="B82" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>136996243</v>
       </c>
       <c r="B83" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11646,7 +11646,7 @@
         <v>136996244</v>
       </c>
       <c r="B84" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>136996245</v>
       </c>
       <c r="B85" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         <v>136996246</v>
       </c>
       <c r="B86" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>136996247</v>
       </c>
       <c r="B87" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         <v>136996248</v>
       </c>
       <c r="B88" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         <v>136996249</v>
       </c>
       <c r="B89" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>136996204</v>
       </c>
       <c r="B94" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -13114,7 +13114,7 @@
         <v>136996205</v>
       </c>
       <c r="B95" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -13249,7 +13249,7 @@
         <v>136996207</v>
       </c>
       <c r="B96" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>136996208</v>
       </c>
       <c r="B97" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
         <v>136996209</v>
       </c>
       <c r="B98" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>136996210</v>
       </c>
       <c r="B99" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13789,7 +13789,7 @@
         <v>136996211</v>
       </c>
       <c r="B100" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>136996212</v>
       </c>
       <c r="B101" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>136996213</v>
       </c>
       <c r="B102" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>136996214</v>
       </c>
       <c r="B103" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -14329,7 +14329,7 @@
         <v>136996215</v>
       </c>
       <c r="B104" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -14464,7 +14464,7 @@
         <v>136996216</v>
       </c>
       <c r="B105" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -14599,7 +14599,7 @@
         <v>136996218</v>
       </c>
       <c r="B106" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14734,7 +14734,7 @@
         <v>136996335</v>
       </c>
       <c r="B107" t="n">
-        <v>80614</v>
+        <v>80627</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>136996250</v>
       </c>
       <c r="B109" t="n">
-        <v>80615</v>
+        <v>80628</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>136996251</v>
       </c>
       <c r="B110" t="n">
-        <v>80615</v>
+        <v>80628</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>136996252</v>
       </c>
       <c r="B111" t="n">
-        <v>80615</v>
+        <v>80628</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         <v>136996253</v>
       </c>
       <c r="B112" t="n">
-        <v>80615</v>
+        <v>80628</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>136996254</v>
       </c>
       <c r="B113" t="n">
-        <v>80615</v>
+        <v>80628</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
         <v>136996255</v>
       </c>
       <c r="B114" t="n">
-        <v>80615</v>
+        <v>80628</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -15825,7 +15825,7 @@
         <v>136996256</v>
       </c>
       <c r="B115" t="n">
-        <v>80615</v>
+        <v>80628</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>136996257</v>
       </c>
       <c r="B116" t="n">
-        <v>80615</v>
+        <v>80628</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>136996258</v>
       </c>
       <c r="B117" t="n">
-        <v>80615</v>
+        <v>80628</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>136996259</v>
       </c>
       <c r="B118" t="n">
-        <v>80615</v>
+        <v>80628</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>136996260</v>
       </c>
       <c r="B119" t="n">
-        <v>80615</v>
+        <v>80628</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>136996261</v>
       </c>
       <c r="B120" t="n">
-        <v>80615</v>
+        <v>80628</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>136996262</v>
       </c>
       <c r="B121" t="n">
-        <v>80615</v>
+        <v>80628</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>136996263</v>
       </c>
       <c r="B122" t="n">
-        <v>80615</v>
+        <v>80628</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>136996264</v>
       </c>
       <c r="B123" t="n">
-        <v>80615</v>
+        <v>80628</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>136996265</v>
       </c>
       <c r="B124" t="n">
-        <v>80615</v>
+        <v>80628</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -17195,7 +17195,7 @@
         <v>136996266</v>
       </c>
       <c r="B125" t="n">
-        <v>80615</v>
+        <v>80628</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -17330,7 +17330,7 @@
         <v>136996267</v>
       </c>
       <c r="B126" t="n">
-        <v>80615</v>
+        <v>80628</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -17465,7 +17465,7 @@
         <v>136996268</v>
       </c>
       <c r="B127" t="n">
-        <v>80615</v>
+        <v>80628</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -18830,7 +18830,7 @@
         <v>136996197</v>
       </c>
       <c r="B137" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -18975,7 +18975,7 @@
         <v>136996200</v>
       </c>
       <c r="B138" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -19103,7 +19103,7 @@
         <v>136996201</v>
       </c>
       <c r="B139" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -19231,7 +19231,7 @@
         <v>136996199</v>
       </c>
       <c r="B140" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>136996276</v>
       </c>
       <c r="B141" t="n">
-        <v>58112</v>
+        <v>58125</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>136996269</v>
       </c>
       <c r="B144" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
         <v>136996270</v>
       </c>
       <c r="B145" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>136996271</v>
       </c>
       <c r="B146" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>136996274</v>
       </c>
       <c r="B147" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>136996275</v>
       </c>
       <c r="B148" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>136996278</v>
       </c>
       <c r="B150" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>136996279</v>
       </c>
       <c r="B151" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -20695,7 +20695,7 @@
         <v>136996282</v>
       </c>
       <c r="B152" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>136996283</v>
       </c>
       <c r="B153" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -20953,7 +20953,7 @@
         <v>136996221</v>
       </c>
       <c r="B154" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>

--- a/artfynd/A 17248-2026 artfynd.xlsx
+++ b/artfynd/A 17248-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136996334</v>
       </c>
       <c r="B2" t="n">
-        <v>89504</v>
+        <v>89506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>136996333</v>
       </c>
       <c r="B3" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>136996220</v>
       </c>
       <c r="B4" t="n">
-        <v>80617</v>
+        <v>80619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>136996284</v>
       </c>
       <c r="B22" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>136996285</v>
       </c>
       <c r="B23" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>136996286</v>
       </c>
       <c r="B24" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>136996287</v>
       </c>
       <c r="B25" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>136996288</v>
       </c>
       <c r="B26" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>136996289</v>
       </c>
       <c r="B27" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>136996290</v>
       </c>
       <c r="B28" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>136996292</v>
       </c>
       <c r="B29" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>136996293</v>
       </c>
       <c r="B30" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         <v>136996294</v>
       </c>
       <c r="B31" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>136996295</v>
       </c>
       <c r="B32" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>136996297</v>
       </c>
       <c r="B33" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4913,7 +4913,7 @@
         <v>136996298</v>
       </c>
       <c r="B34" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
         <v>136996299</v>
       </c>
       <c r="B35" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>136996300</v>
       </c>
       <c r="B36" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>136996301</v>
       </c>
       <c r="B37" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>136996302</v>
       </c>
       <c r="B38" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>136996303</v>
       </c>
       <c r="B39" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>136996304</v>
       </c>
       <c r="B40" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>136996305</v>
       </c>
       <c r="B41" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>136996306</v>
       </c>
       <c r="B42" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>136996307</v>
       </c>
       <c r="B43" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>136996308</v>
       </c>
       <c r="B44" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>136996309</v>
       </c>
       <c r="B45" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>136996310</v>
       </c>
       <c r="B46" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>136996311</v>
       </c>
       <c r="B47" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>136996313</v>
       </c>
       <c r="B48" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>136996314</v>
       </c>
       <c r="B49" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>136996315</v>
       </c>
       <c r="B50" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>136996316</v>
       </c>
       <c r="B51" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>136996317</v>
       </c>
       <c r="B52" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>136996318</v>
       </c>
       <c r="B53" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>136996319</v>
       </c>
       <c r="B54" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>136996320</v>
       </c>
       <c r="B55" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>136996321</v>
       </c>
       <c r="B56" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>136996322</v>
       </c>
       <c r="B57" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>136996323</v>
       </c>
       <c r="B58" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>136996324</v>
       </c>
       <c r="B59" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>136996325</v>
       </c>
       <c r="B60" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>136996326</v>
       </c>
       <c r="B61" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>136996332</v>
       </c>
       <c r="B62" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>136996223</v>
       </c>
       <c r="B65" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>136996224</v>
       </c>
       <c r="B66" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>136996225</v>
       </c>
       <c r="B67" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>136996226</v>
       </c>
       <c r="B68" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>136996228</v>
       </c>
       <c r="B69" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>136996229</v>
       </c>
       <c r="B70" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9891,7 +9891,7 @@
         <v>136996230</v>
       </c>
       <c r="B71" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>136996231</v>
       </c>
       <c r="B72" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>136996232</v>
       </c>
       <c r="B73" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>136996233</v>
       </c>
       <c r="B74" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>136996234</v>
       </c>
       <c r="B75" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>136996235</v>
       </c>
       <c r="B76" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>136996236</v>
       </c>
       <c r="B77" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>136996237</v>
       </c>
       <c r="B78" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10969,7 +10969,7 @@
         <v>136996239</v>
       </c>
       <c r="B79" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -11100,7 +11100,7 @@
         <v>136996240</v>
       </c>
       <c r="B80" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11235,7 +11235,7 @@
         <v>136996241</v>
       </c>
       <c r="B81" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -11371,7 +11371,7 @@
         <v>136996242</v>
       </c>
       <c r="B82" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>136996243</v>
       </c>
       <c r="B83" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11646,7 +11646,7 @@
         <v>136996244</v>
       </c>
       <c r="B84" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>136996245</v>
       </c>
       <c r="B85" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         <v>136996246</v>
       </c>
       <c r="B86" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>136996247</v>
       </c>
       <c r="B87" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         <v>136996248</v>
       </c>
       <c r="B88" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         <v>136996249</v>
       </c>
       <c r="B89" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>136996204</v>
       </c>
       <c r="B94" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -13114,7 +13114,7 @@
         <v>136996205</v>
       </c>
       <c r="B95" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -13249,7 +13249,7 @@
         <v>136996207</v>
       </c>
       <c r="B96" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>136996208</v>
       </c>
       <c r="B97" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
         <v>136996209</v>
       </c>
       <c r="B98" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>136996210</v>
       </c>
       <c r="B99" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13789,7 +13789,7 @@
         <v>136996211</v>
       </c>
       <c r="B100" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>136996212</v>
       </c>
       <c r="B101" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>136996213</v>
       </c>
       <c r="B102" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>136996214</v>
       </c>
       <c r="B103" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -14329,7 +14329,7 @@
         <v>136996215</v>
       </c>
       <c r="B104" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -14464,7 +14464,7 @@
         <v>136996216</v>
       </c>
       <c r="B105" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -14599,7 +14599,7 @@
         <v>136996218</v>
       </c>
       <c r="B106" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14734,7 +14734,7 @@
         <v>136996335</v>
       </c>
       <c r="B107" t="n">
-        <v>80627</v>
+        <v>80629</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>136996250</v>
       </c>
       <c r="B109" t="n">
-        <v>80628</v>
+        <v>80630</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>136996251</v>
       </c>
       <c r="B110" t="n">
-        <v>80628</v>
+        <v>80630</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>136996252</v>
       </c>
       <c r="B111" t="n">
-        <v>80628</v>
+        <v>80630</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         <v>136996253</v>
       </c>
       <c r="B112" t="n">
-        <v>80628</v>
+        <v>80630</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>136996254</v>
       </c>
       <c r="B113" t="n">
-        <v>80628</v>
+        <v>80630</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
         <v>136996255</v>
       </c>
       <c r="B114" t="n">
-        <v>80628</v>
+        <v>80630</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -15825,7 +15825,7 @@
         <v>136996256</v>
       </c>
       <c r="B115" t="n">
-        <v>80628</v>
+        <v>80630</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>136996257</v>
       </c>
       <c r="B116" t="n">
-        <v>80628</v>
+        <v>80630</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>136996258</v>
       </c>
       <c r="B117" t="n">
-        <v>80628</v>
+        <v>80630</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>136996259</v>
       </c>
       <c r="B118" t="n">
-        <v>80628</v>
+        <v>80630</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>136996260</v>
       </c>
       <c r="B119" t="n">
-        <v>80628</v>
+        <v>80630</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>136996261</v>
       </c>
       <c r="B120" t="n">
-        <v>80628</v>
+        <v>80630</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>136996262</v>
       </c>
       <c r="B121" t="n">
-        <v>80628</v>
+        <v>80630</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>136996263</v>
       </c>
       <c r="B122" t="n">
-        <v>80628</v>
+        <v>80630</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>136996264</v>
       </c>
       <c r="B123" t="n">
-        <v>80628</v>
+        <v>80630</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>136996265</v>
       </c>
       <c r="B124" t="n">
-        <v>80628</v>
+        <v>80630</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -17195,7 +17195,7 @@
         <v>136996266</v>
       </c>
       <c r="B125" t="n">
-        <v>80628</v>
+        <v>80630</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -17330,7 +17330,7 @@
         <v>136996267</v>
       </c>
       <c r="B126" t="n">
-        <v>80628</v>
+        <v>80630</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -17465,7 +17465,7 @@
         <v>136996268</v>
       </c>
       <c r="B127" t="n">
-        <v>80628</v>
+        <v>80630</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -18830,7 +18830,7 @@
         <v>136996197</v>
       </c>
       <c r="B137" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -18975,7 +18975,7 @@
         <v>136996200</v>
       </c>
       <c r="B138" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -19103,7 +19103,7 @@
         <v>136996201</v>
       </c>
       <c r="B139" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -19231,7 +19231,7 @@
         <v>136996199</v>
       </c>
       <c r="B140" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>136996276</v>
       </c>
       <c r="B141" t="n">
-        <v>58125</v>
+        <v>58127</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>136996269</v>
       </c>
       <c r="B144" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
         <v>136996270</v>
       </c>
       <c r="B145" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>136996271</v>
       </c>
       <c r="B146" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>136996274</v>
       </c>
       <c r="B147" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>136996275</v>
       </c>
       <c r="B148" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>136996278</v>
       </c>
       <c r="B150" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>136996279</v>
       </c>
       <c r="B151" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -20695,7 +20695,7 @@
         <v>136996282</v>
       </c>
       <c r="B152" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>136996283</v>
       </c>
       <c r="B153" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -20953,7 +20953,7 @@
         <v>136996221</v>
       </c>
       <c r="B154" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>

--- a/artfynd/A 17248-2026 artfynd.xlsx
+++ b/artfynd/A 17248-2026 artfynd.xlsx
@@ -710,11 +710,7 @@
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -855,11 +851,7 @@
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -6008,11 +6000,7 @@
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -7881,11 +7869,7 @@
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -9088,11 +9072,7 @@
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -9223,11 +9203,7 @@
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -9358,11 +9334,7 @@
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -9498,11 +9470,7 @@
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -9638,11 +9606,7 @@
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -9778,11 +9742,7 @@
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -10049,11 +10009,7 @@
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -10189,11 +10145,7 @@
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -10324,11 +10276,7 @@
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -10459,11 +10407,7 @@
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -10594,11 +10538,7 @@
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -11127,11 +11067,7 @@
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -11398,11 +11334,7 @@
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -11533,11 +11465,7 @@
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -12076,11 +12004,7 @@
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -13006,11 +12930,7 @@
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -13141,11 +13061,7 @@
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -13276,11 +13192,7 @@
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -13411,11 +13323,7 @@
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -13546,11 +13454,7 @@
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
@@ -13681,11 +13585,7 @@
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
@@ -13816,11 +13716,7 @@
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -13951,11 +13847,7 @@
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -14086,11 +13978,7 @@
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
@@ -14221,11 +14109,7 @@
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
@@ -14356,11 +14240,7 @@
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
@@ -14491,11 +14371,7 @@
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
@@ -14626,11 +14502,7 @@
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
@@ -14761,11 +14633,7 @@
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
@@ -15031,11 +14899,7 @@
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
@@ -15171,11 +15035,7 @@
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -15442,11 +15302,7 @@
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -15582,11 +15438,7 @@
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
@@ -15717,11 +15569,7 @@
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
@@ -15852,11 +15700,7 @@
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -15987,11 +15831,7 @@
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -16122,11 +15962,7 @@
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -16262,11 +16098,7 @@
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
@@ -16397,11 +16229,7 @@
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K119" t="inlineStr"/>
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
@@ -16532,11 +16360,7 @@
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K120" t="inlineStr"/>
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
@@ -16672,11 +16496,7 @@
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K121" t="inlineStr"/>
       <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
@@ -16807,11 +16627,7 @@
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K122" t="inlineStr"/>
       <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
@@ -16947,11 +16763,7 @@
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K123" t="inlineStr"/>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
@@ -17087,11 +16899,7 @@
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -17222,11 +17030,7 @@
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K125" t="inlineStr"/>
       <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
@@ -17357,11 +17161,7 @@
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K126" t="inlineStr"/>
       <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
@@ -17492,11 +17292,7 @@
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K127" t="inlineStr"/>
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
@@ -18858,11 +18654,7 @@
       <c r="I137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M137" t="inlineStr"/>
       <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
@@ -19007,11 +18799,7 @@
       </c>
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -19135,11 +18923,7 @@
       </c>
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M139" t="inlineStr"/>
       <c r="N139" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -19263,11 +19047,7 @@
       </c>
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -19391,11 +19171,7 @@
       </c>
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M141" t="inlineStr"/>
       <c r="N141" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -19751,11 +19527,7 @@
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr"/>
       <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
@@ -19867,11 +19639,7 @@
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr"/>
       <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
@@ -19983,11 +19751,7 @@
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr"/>
       <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
@@ -20099,11 +19863,7 @@
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr"/>
       <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
@@ -20215,11 +19975,7 @@
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr"/>
       <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
@@ -20472,11 +20228,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr"/>
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
@@ -20601,11 +20353,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr"/>
       <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
@@ -20730,11 +20478,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr"/>
       <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
@@ -20859,11 +20603,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr"/>
       <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">

--- a/artfynd/A 17248-2026 artfynd.xlsx
+++ b/artfynd/A 17248-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136996334</v>
       </c>
       <c r="B2" t="n">
-        <v>89506</v>
+        <v>89509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>136996269</v>
       </c>
       <c r="B144" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         <v>136996270</v>
       </c>
       <c r="B145" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>136996271</v>
       </c>
       <c r="B146" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>136996274</v>
       </c>
       <c r="B147" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>136996275</v>
       </c>
       <c r="B148" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -20193,7 +20193,7 @@
         <v>136996278</v>
       </c>
       <c r="B150" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>136996279</v>
       </c>
       <c r="B151" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>136996282</v>
       </c>
       <c r="B152" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>136996283</v>
       </c>
       <c r="B153" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>136996221</v>
       </c>
       <c r="B154" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>

--- a/artfynd/A 17248-2026 artfynd.xlsx
+++ b/artfynd/A 17248-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136996334</v>
       </c>
       <c r="B2" t="n">
-        <v>89509</v>
+        <v>89519</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>136996333</v>
       </c>
       <c r="B3" t="n">
-        <v>83371</v>
+        <v>83381</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>136996220</v>
       </c>
       <c r="B4" t="n">
-        <v>80619</v>
+        <v>80629</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>136996284</v>
       </c>
       <c r="B22" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>136996285</v>
       </c>
       <c r="B23" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>136996286</v>
       </c>
       <c r="B24" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>136996287</v>
       </c>
       <c r="B25" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>136996288</v>
       </c>
       <c r="B26" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v>136996289</v>
       </c>
       <c r="B27" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>136996290</v>
       </c>
       <c r="B28" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>136996292</v>
       </c>
       <c r="B29" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>136996293</v>
       </c>
       <c r="B30" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>136996294</v>
       </c>
       <c r="B31" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>136996295</v>
       </c>
       <c r="B32" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>136996297</v>
       </c>
       <c r="B33" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>136996298</v>
       </c>
       <c r="B34" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>136996299</v>
       </c>
       <c r="B35" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>136996300</v>
       </c>
       <c r="B36" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>136996301</v>
       </c>
       <c r="B37" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         <v>136996302</v>
       </c>
       <c r="B38" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>136996303</v>
       </c>
       <c r="B39" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>136996304</v>
       </c>
       <c r="B40" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>136996305</v>
       </c>
       <c r="B41" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>136996306</v>
       </c>
       <c r="B42" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>136996307</v>
       </c>
       <c r="B43" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>136996308</v>
       </c>
       <c r="B44" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>136996309</v>
       </c>
       <c r="B45" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>136996310</v>
       </c>
       <c r="B46" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>136996311</v>
       </c>
       <c r="B47" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>136996313</v>
       </c>
       <c r="B48" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>136996314</v>
       </c>
       <c r="B49" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>136996315</v>
       </c>
       <c r="B50" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>136996316</v>
       </c>
       <c r="B51" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>136996317</v>
       </c>
       <c r="B52" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>136996318</v>
       </c>
       <c r="B53" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         <v>136996319</v>
       </c>
       <c r="B54" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         <v>136996320</v>
       </c>
       <c r="B55" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>136996321</v>
       </c>
       <c r="B56" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>136996322</v>
       </c>
       <c r="B57" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>136996323</v>
       </c>
       <c r="B58" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         <v>136996324</v>
       </c>
       <c r="B59" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>136996325</v>
       </c>
       <c r="B60" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>136996326</v>
       </c>
       <c r="B61" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>136996332</v>
       </c>
       <c r="B62" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>136996223</v>
       </c>
       <c r="B65" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9176,7 +9176,7 @@
         <v>136996224</v>
       </c>
       <c r="B66" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>136996225</v>
       </c>
       <c r="B67" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>136996226</v>
       </c>
       <c r="B68" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>136996228</v>
       </c>
       <c r="B69" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>136996229</v>
       </c>
       <c r="B70" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9851,7 +9851,7 @@
         <v>136996230</v>
       </c>
       <c r="B71" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>136996231</v>
       </c>
       <c r="B72" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -10118,7 +10118,7 @@
         <v>136996232</v>
       </c>
       <c r="B73" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>136996233</v>
       </c>
       <c r="B74" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>136996234</v>
       </c>
       <c r="B75" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>136996235</v>
       </c>
       <c r="B76" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>136996236</v>
       </c>
       <c r="B77" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         <v>136996237</v>
       </c>
       <c r="B78" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>136996239</v>
       </c>
       <c r="B79" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>136996240</v>
       </c>
       <c r="B80" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>136996241</v>
       </c>
       <c r="B81" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -11307,7 +11307,7 @@
         <v>136996242</v>
       </c>
       <c r="B82" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>136996243</v>
       </c>
       <c r="B83" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>136996244</v>
       </c>
       <c r="B84" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>136996245</v>
       </c>
       <c r="B85" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>136996246</v>
       </c>
       <c r="B86" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11977,7 +11977,7 @@
         <v>136996247</v>
       </c>
       <c r="B87" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>136996248</v>
       </c>
       <c r="B88" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -12249,7 +12249,7 @@
         <v>136996249</v>
       </c>
       <c r="B89" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>136996204</v>
       </c>
       <c r="B94" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -13034,7 +13034,7 @@
         <v>136996205</v>
       </c>
       <c r="B95" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -13165,7 +13165,7 @@
         <v>136996207</v>
       </c>
       <c r="B96" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -13296,7 +13296,7 @@
         <v>136996208</v>
       </c>
       <c r="B97" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>136996209</v>
       </c>
       <c r="B98" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
         <v>136996210</v>
       </c>
       <c r="B99" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>136996211</v>
       </c>
       <c r="B100" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>136996212</v>
       </c>
       <c r="B101" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>136996213</v>
       </c>
       <c r="B102" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -14082,7 +14082,7 @@
         <v>136996214</v>
       </c>
       <c r="B103" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>136996215</v>
       </c>
       <c r="B104" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>136996216</v>
       </c>
       <c r="B105" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>136996218</v>
       </c>
       <c r="B106" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>136996335</v>
       </c>
       <c r="B107" t="n">
-        <v>80629</v>
+        <v>80639</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>136996250</v>
       </c>
       <c r="B109" t="n">
-        <v>80630</v>
+        <v>80640</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>136996251</v>
       </c>
       <c r="B110" t="n">
-        <v>80630</v>
+        <v>80640</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>136996252</v>
       </c>
       <c r="B111" t="n">
-        <v>80630</v>
+        <v>80640</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
         <v>136996253</v>
       </c>
       <c r="B112" t="n">
-        <v>80630</v>
+        <v>80640</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>136996254</v>
       </c>
       <c r="B113" t="n">
-        <v>80630</v>
+        <v>80640</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -15542,7 +15542,7 @@
         <v>136996255</v>
       </c>
       <c r="B114" t="n">
-        <v>80630</v>
+        <v>80640</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>136996256</v>
       </c>
       <c r="B115" t="n">
-        <v>80630</v>
+        <v>80640</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>136996257</v>
       </c>
       <c r="B116" t="n">
-        <v>80630</v>
+        <v>80640</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -15935,7 +15935,7 @@
         <v>136996258</v>
       </c>
       <c r="B117" t="n">
-        <v>80630</v>
+        <v>80640</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -16071,7 +16071,7 @@
         <v>136996259</v>
       </c>
       <c r="B118" t="n">
-        <v>80630</v>
+        <v>80640</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>136996260</v>
       </c>
       <c r="B119" t="n">
-        <v>80630</v>
+        <v>80640</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -16333,7 +16333,7 @@
         <v>136996261</v>
       </c>
       <c r="B120" t="n">
-        <v>80630</v>
+        <v>80640</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
         <v>136996262</v>
       </c>
       <c r="B121" t="n">
-        <v>80630</v>
+        <v>80640</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -16600,7 +16600,7 @@
         <v>136996263</v>
       </c>
       <c r="B122" t="n">
-        <v>80630</v>
+        <v>80640</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>136996264</v>
       </c>
       <c r="B123" t="n">
-        <v>80630</v>
+        <v>80640</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -16872,7 +16872,7 @@
         <v>136996265</v>
       </c>
       <c r="B124" t="n">
-        <v>80630</v>
+        <v>80640</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -17003,7 +17003,7 @@
         <v>136996266</v>
       </c>
       <c r="B125" t="n">
-        <v>80630</v>
+        <v>80640</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -17134,7 +17134,7 @@
         <v>136996267</v>
       </c>
       <c r="B126" t="n">
-        <v>80630</v>
+        <v>80640</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         <v>136996268</v>
       </c>
       <c r="B127" t="n">
-        <v>80630</v>
+        <v>80640</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -18626,7 +18626,7 @@
         <v>136996197</v>
       </c>
       <c r="B137" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>136996200</v>
       </c>
       <c r="B138" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -18891,7 +18891,7 @@
         <v>136996201</v>
       </c>
       <c r="B139" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -19015,7 +19015,7 @@
         <v>136996199</v>
       </c>
       <c r="B140" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>136996276</v>
       </c>
       <c r="B141" t="n">
-        <v>58127</v>
+        <v>58137</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>136996269</v>
       </c>
       <c r="B144" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         <v>136996270</v>
       </c>
       <c r="B145" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>136996271</v>
       </c>
       <c r="B146" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>136996274</v>
       </c>
       <c r="B147" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>136996275</v>
       </c>
       <c r="B148" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -20193,7 +20193,7 @@
         <v>136996278</v>
       </c>
       <c r="B150" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>136996279</v>
       </c>
       <c r="B151" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>136996282</v>
       </c>
       <c r="B152" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>136996283</v>
       </c>
       <c r="B153" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>136996221</v>
       </c>
       <c r="B154" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>

--- a/artfynd/A 17248-2026 artfynd.xlsx
+++ b/artfynd/A 17248-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136996334</v>
       </c>
       <c r="B2" t="n">
-        <v>89519</v>
+        <v>89520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>136996269</v>
       </c>
       <c r="B144" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         <v>136996270</v>
       </c>
       <c r="B145" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>136996271</v>
       </c>
       <c r="B146" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>136996274</v>
       </c>
       <c r="B147" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>136996275</v>
       </c>
       <c r="B148" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -20193,7 +20193,7 @@
         <v>136996278</v>
       </c>
       <c r="B150" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>136996279</v>
       </c>
       <c r="B151" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>136996282</v>
       </c>
       <c r="B152" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>136996283</v>
       </c>
       <c r="B153" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>136996221</v>
       </c>
       <c r="B154" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>

--- a/artfynd/A 17248-2026 artfynd.xlsx
+++ b/artfynd/A 17248-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136996334</v>
       </c>
       <c r="B2" t="n">
-        <v>89520</v>
+        <v>89523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>136996333</v>
       </c>
       <c r="B3" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>136996220</v>
       </c>
       <c r="B4" t="n">
-        <v>80629</v>
+        <v>80632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>136996284</v>
       </c>
       <c r="B22" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>136996285</v>
       </c>
       <c r="B23" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>136996286</v>
       </c>
       <c r="B24" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>136996287</v>
       </c>
       <c r="B25" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>136996288</v>
       </c>
       <c r="B26" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v>136996289</v>
       </c>
       <c r="B27" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>136996290</v>
       </c>
       <c r="B28" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>136996292</v>
       </c>
       <c r="B29" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>136996293</v>
       </c>
       <c r="B30" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>136996294</v>
       </c>
       <c r="B31" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>136996295</v>
       </c>
       <c r="B32" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>136996297</v>
       </c>
       <c r="B33" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>136996298</v>
       </c>
       <c r="B34" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>136996299</v>
       </c>
       <c r="B35" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>136996300</v>
       </c>
       <c r="B36" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>136996301</v>
       </c>
       <c r="B37" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         <v>136996302</v>
       </c>
       <c r="B38" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>136996303</v>
       </c>
       <c r="B39" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>136996304</v>
       </c>
       <c r="B40" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>136996305</v>
       </c>
       <c r="B41" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>136996306</v>
       </c>
       <c r="B42" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>136996307</v>
       </c>
       <c r="B43" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>136996308</v>
       </c>
       <c r="B44" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>136996309</v>
       </c>
       <c r="B45" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>136996310</v>
       </c>
       <c r="B46" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>136996311</v>
       </c>
       <c r="B47" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>136996313</v>
       </c>
       <c r="B48" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>136996314</v>
       </c>
       <c r="B49" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>136996315</v>
       </c>
       <c r="B50" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>136996316</v>
       </c>
       <c r="B51" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>136996317</v>
       </c>
       <c r="B52" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>136996318</v>
       </c>
       <c r="B53" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         <v>136996319</v>
       </c>
       <c r="B54" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         <v>136996320</v>
       </c>
       <c r="B55" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>136996321</v>
       </c>
       <c r="B56" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>136996322</v>
       </c>
       <c r="B57" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>136996323</v>
       </c>
       <c r="B58" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         <v>136996324</v>
       </c>
       <c r="B59" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>136996325</v>
       </c>
       <c r="B60" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>136996326</v>
       </c>
       <c r="B61" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>136996332</v>
       </c>
       <c r="B62" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>136996223</v>
       </c>
       <c r="B65" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9176,7 +9176,7 @@
         <v>136996224</v>
       </c>
       <c r="B66" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>136996225</v>
       </c>
       <c r="B67" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>136996226</v>
       </c>
       <c r="B68" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>136996228</v>
       </c>
       <c r="B69" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>136996229</v>
       </c>
       <c r="B70" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9851,7 +9851,7 @@
         <v>136996230</v>
       </c>
       <c r="B71" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>136996231</v>
       </c>
       <c r="B72" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -10118,7 +10118,7 @@
         <v>136996232</v>
       </c>
       <c r="B73" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>136996233</v>
       </c>
       <c r="B74" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>136996234</v>
       </c>
       <c r="B75" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>136996235</v>
       </c>
       <c r="B76" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>136996236</v>
       </c>
       <c r="B77" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         <v>136996237</v>
       </c>
       <c r="B78" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>136996239</v>
       </c>
       <c r="B79" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>136996240</v>
       </c>
       <c r="B80" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>136996241</v>
       </c>
       <c r="B81" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -11307,7 +11307,7 @@
         <v>136996242</v>
       </c>
       <c r="B82" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>136996243</v>
       </c>
       <c r="B83" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>136996244</v>
       </c>
       <c r="B84" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>136996245</v>
       </c>
       <c r="B85" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>136996246</v>
       </c>
       <c r="B86" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11977,7 +11977,7 @@
         <v>136996247</v>
       </c>
       <c r="B87" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>136996248</v>
       </c>
       <c r="B88" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -12249,7 +12249,7 @@
         <v>136996249</v>
       </c>
       <c r="B89" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>136996204</v>
       </c>
       <c r="B94" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -13034,7 +13034,7 @@
         <v>136996205</v>
       </c>
       <c r="B95" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -13165,7 +13165,7 @@
         <v>136996207</v>
       </c>
       <c r="B96" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -13296,7 +13296,7 @@
         <v>136996208</v>
       </c>
       <c r="B97" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>136996209</v>
       </c>
       <c r="B98" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
         <v>136996210</v>
       </c>
       <c r="B99" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>136996211</v>
       </c>
       <c r="B100" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>136996212</v>
       </c>
       <c r="B101" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>136996213</v>
       </c>
       <c r="B102" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -14082,7 +14082,7 @@
         <v>136996214</v>
       </c>
       <c r="B103" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>136996215</v>
       </c>
       <c r="B104" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>136996216</v>
       </c>
       <c r="B105" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>136996218</v>
       </c>
       <c r="B106" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>136996335</v>
       </c>
       <c r="B107" t="n">
-        <v>80639</v>
+        <v>80642</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>136996250</v>
       </c>
       <c r="B109" t="n">
-        <v>80640</v>
+        <v>80643</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>136996251</v>
       </c>
       <c r="B110" t="n">
-        <v>80640</v>
+        <v>80643</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>136996252</v>
       </c>
       <c r="B111" t="n">
-        <v>80640</v>
+        <v>80643</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
         <v>136996253</v>
       </c>
       <c r="B112" t="n">
-        <v>80640</v>
+        <v>80643</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>136996254</v>
       </c>
       <c r="B113" t="n">
-        <v>80640</v>
+        <v>80643</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -15542,7 +15542,7 @@
         <v>136996255</v>
       </c>
       <c r="B114" t="n">
-        <v>80640</v>
+        <v>80643</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>136996256</v>
       </c>
       <c r="B115" t="n">
-        <v>80640</v>
+        <v>80643</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>136996257</v>
       </c>
       <c r="B116" t="n">
-        <v>80640</v>
+        <v>80643</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -15935,7 +15935,7 @@
         <v>136996258</v>
       </c>
       <c r="B117" t="n">
-        <v>80640</v>
+        <v>80643</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -16071,7 +16071,7 @@
         <v>136996259</v>
       </c>
       <c r="B118" t="n">
-        <v>80640</v>
+        <v>80643</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>136996260</v>
       </c>
       <c r="B119" t="n">
-        <v>80640</v>
+        <v>80643</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -16333,7 +16333,7 @@
         <v>136996261</v>
       </c>
       <c r="B120" t="n">
-        <v>80640</v>
+        <v>80643</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
         <v>136996262</v>
       </c>
       <c r="B121" t="n">
-        <v>80640</v>
+        <v>80643</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -16600,7 +16600,7 @@
         <v>136996263</v>
       </c>
       <c r="B122" t="n">
-        <v>80640</v>
+        <v>80643</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>136996264</v>
       </c>
       <c r="B123" t="n">
-        <v>80640</v>
+        <v>80643</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -16872,7 +16872,7 @@
         <v>136996265</v>
       </c>
       <c r="B124" t="n">
-        <v>80640</v>
+        <v>80643</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -17003,7 +17003,7 @@
         <v>136996266</v>
       </c>
       <c r="B125" t="n">
-        <v>80640</v>
+        <v>80643</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -17134,7 +17134,7 @@
         <v>136996267</v>
       </c>
       <c r="B126" t="n">
-        <v>80640</v>
+        <v>80643</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         <v>136996268</v>
       </c>
       <c r="B127" t="n">
-        <v>80640</v>
+        <v>80643</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -18626,7 +18626,7 @@
         <v>136996197</v>
       </c>
       <c r="B137" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>136996200</v>
       </c>
       <c r="B138" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -18891,7 +18891,7 @@
         <v>136996201</v>
       </c>
       <c r="B139" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -19015,7 +19015,7 @@
         <v>136996199</v>
       </c>
       <c r="B140" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>136996276</v>
       </c>
       <c r="B141" t="n">
-        <v>58137</v>
+        <v>58138</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>136996269</v>
       </c>
       <c r="B144" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         <v>136996270</v>
       </c>
       <c r="B145" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>136996271</v>
       </c>
       <c r="B146" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>136996274</v>
       </c>
       <c r="B147" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>136996275</v>
       </c>
       <c r="B148" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -20193,7 +20193,7 @@
         <v>136996278</v>
       </c>
       <c r="B150" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>136996279</v>
       </c>
       <c r="B151" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>136996282</v>
       </c>
       <c r="B152" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>136996283</v>
       </c>
       <c r="B153" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>136996221</v>
       </c>
       <c r="B154" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>

--- a/artfynd/A 17248-2026 artfynd.xlsx
+++ b/artfynd/A 17248-2026 artfynd.xlsx
@@ -19500,7 +19500,7 @@
         <v>136996269</v>
       </c>
       <c r="B144" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         <v>136996270</v>
       </c>
       <c r="B145" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>136996271</v>
       </c>
       <c r="B146" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>136996274</v>
       </c>
       <c r="B147" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>136996275</v>
       </c>
       <c r="B148" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -20193,7 +20193,7 @@
         <v>136996278</v>
       </c>
       <c r="B150" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>136996279</v>
       </c>
       <c r="B151" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>136996282</v>
       </c>
       <c r="B152" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>136996283</v>
       </c>
       <c r="B153" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>136996221</v>
       </c>
       <c r="B154" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>

--- a/artfynd/A 17248-2026 artfynd.xlsx
+++ b/artfynd/A 17248-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136996334</v>
       </c>
       <c r="B2" t="n">
-        <v>89523</v>
+        <v>89528</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>136996333</v>
       </c>
       <c r="B3" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>136996220</v>
       </c>
       <c r="B4" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>136996284</v>
       </c>
       <c r="B22" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>136996285</v>
       </c>
       <c r="B23" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>136996286</v>
       </c>
       <c r="B24" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>136996287</v>
       </c>
       <c r="B25" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>136996288</v>
       </c>
       <c r="B26" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v>136996289</v>
       </c>
       <c r="B27" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>136996290</v>
       </c>
       <c r="B28" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>136996292</v>
       </c>
       <c r="B29" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>136996293</v>
       </c>
       <c r="B30" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>136996294</v>
       </c>
       <c r="B31" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>136996295</v>
       </c>
       <c r="B32" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>136996297</v>
       </c>
       <c r="B33" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>136996298</v>
       </c>
       <c r="B34" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>136996299</v>
       </c>
       <c r="B35" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>136996300</v>
       </c>
       <c r="B36" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>136996301</v>
       </c>
       <c r="B37" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         <v>136996302</v>
       </c>
       <c r="B38" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>136996303</v>
       </c>
       <c r="B39" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>136996304</v>
       </c>
       <c r="B40" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>136996305</v>
       </c>
       <c r="B41" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>136996306</v>
       </c>
       <c r="B42" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>136996307</v>
       </c>
       <c r="B43" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>136996308</v>
       </c>
       <c r="B44" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>136996309</v>
       </c>
       <c r="B45" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>136996310</v>
       </c>
       <c r="B46" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>136996311</v>
       </c>
       <c r="B47" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>136996313</v>
       </c>
       <c r="B48" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>136996314</v>
       </c>
       <c r="B49" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>136996315</v>
       </c>
       <c r="B50" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>136996316</v>
       </c>
       <c r="B51" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>136996317</v>
       </c>
       <c r="B52" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>136996318</v>
       </c>
       <c r="B53" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         <v>136996319</v>
       </c>
       <c r="B54" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         <v>136996320</v>
       </c>
       <c r="B55" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>136996321</v>
       </c>
       <c r="B56" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>136996322</v>
       </c>
       <c r="B57" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>136996323</v>
       </c>
       <c r="B58" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         <v>136996324</v>
       </c>
       <c r="B59" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>136996325</v>
       </c>
       <c r="B60" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>136996326</v>
       </c>
       <c r="B61" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>136996332</v>
       </c>
       <c r="B62" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>136996223</v>
       </c>
       <c r="B65" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9176,7 +9176,7 @@
         <v>136996224</v>
       </c>
       <c r="B66" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>136996225</v>
       </c>
       <c r="B67" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>136996226</v>
       </c>
       <c r="B68" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>136996228</v>
       </c>
       <c r="B69" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>136996229</v>
       </c>
       <c r="B70" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9851,7 +9851,7 @@
         <v>136996230</v>
       </c>
       <c r="B71" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>136996231</v>
       </c>
       <c r="B72" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -10118,7 +10118,7 @@
         <v>136996232</v>
       </c>
       <c r="B73" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>136996233</v>
       </c>
       <c r="B74" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>136996234</v>
       </c>
       <c r="B75" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>136996235</v>
       </c>
       <c r="B76" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>136996236</v>
       </c>
       <c r="B77" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         <v>136996237</v>
       </c>
       <c r="B78" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>136996239</v>
       </c>
       <c r="B79" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>136996240</v>
       </c>
       <c r="B80" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>136996241</v>
       </c>
       <c r="B81" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -11307,7 +11307,7 @@
         <v>136996242</v>
       </c>
       <c r="B82" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>136996243</v>
       </c>
       <c r="B83" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>136996244</v>
       </c>
       <c r="B84" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>136996245</v>
       </c>
       <c r="B85" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>136996246</v>
       </c>
       <c r="B86" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11977,7 +11977,7 @@
         <v>136996247</v>
       </c>
       <c r="B87" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>136996248</v>
       </c>
       <c r="B88" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -12249,7 +12249,7 @@
         <v>136996249</v>
       </c>
       <c r="B89" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>136996204</v>
       </c>
       <c r="B94" t="n">
-        <v>80636</v>
+        <v>80641</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -13034,7 +13034,7 @@
         <v>136996205</v>
       </c>
       <c r="B95" t="n">
-        <v>80636</v>
+        <v>80641</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -13165,7 +13165,7 @@
         <v>136996207</v>
       </c>
       <c r="B96" t="n">
-        <v>80636</v>
+        <v>80641</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -13296,7 +13296,7 @@
         <v>136996208</v>
       </c>
       <c r="B97" t="n">
-        <v>80636</v>
+        <v>80641</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>136996209</v>
       </c>
       <c r="B98" t="n">
-        <v>80636</v>
+        <v>80641</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
         <v>136996210</v>
       </c>
       <c r="B99" t="n">
-        <v>80636</v>
+        <v>80641</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>136996211</v>
       </c>
       <c r="B100" t="n">
-        <v>80636</v>
+        <v>80641</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>136996212</v>
       </c>
       <c r="B101" t="n">
-        <v>80636</v>
+        <v>80641</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>136996213</v>
       </c>
       <c r="B102" t="n">
-        <v>80636</v>
+        <v>80641</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -14082,7 +14082,7 @@
         <v>136996214</v>
       </c>
       <c r="B103" t="n">
-        <v>80636</v>
+        <v>80641</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>136996215</v>
       </c>
       <c r="B104" t="n">
-        <v>80636</v>
+        <v>80641</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>136996216</v>
       </c>
       <c r="B105" t="n">
-        <v>80636</v>
+        <v>80641</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>136996218</v>
       </c>
       <c r="B106" t="n">
-        <v>80636</v>
+        <v>80641</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>136996335</v>
       </c>
       <c r="B107" t="n">
-        <v>80642</v>
+        <v>80647</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>136996250</v>
       </c>
       <c r="B109" t="n">
-        <v>80643</v>
+        <v>80648</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>136996251</v>
       </c>
       <c r="B110" t="n">
-        <v>80643</v>
+        <v>80648</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>136996252</v>
       </c>
       <c r="B111" t="n">
-        <v>80643</v>
+        <v>80648</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
         <v>136996253</v>
       </c>
       <c r="B112" t="n">
-        <v>80643</v>
+        <v>80648</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>136996254</v>
       </c>
       <c r="B113" t="n">
-        <v>80643</v>
+        <v>80648</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -15542,7 +15542,7 @@
         <v>136996255</v>
       </c>
       <c r="B114" t="n">
-        <v>80643</v>
+        <v>80648</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>136996256</v>
       </c>
       <c r="B115" t="n">
-        <v>80643</v>
+        <v>80648</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>136996257</v>
       </c>
       <c r="B116" t="n">
-        <v>80643</v>
+        <v>80648</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -15935,7 +15935,7 @@
         <v>136996258</v>
       </c>
       <c r="B117" t="n">
-        <v>80643</v>
+        <v>80648</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -16071,7 +16071,7 @@
         <v>136996259</v>
       </c>
       <c r="B118" t="n">
-        <v>80643</v>
+        <v>80648</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>136996260</v>
       </c>
       <c r="B119" t="n">
-        <v>80643</v>
+        <v>80648</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -16333,7 +16333,7 @@
         <v>136996261</v>
       </c>
       <c r="B120" t="n">
-        <v>80643</v>
+        <v>80648</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
         <v>136996262</v>
       </c>
       <c r="B121" t="n">
-        <v>80643</v>
+        <v>80648</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -16600,7 +16600,7 @@
         <v>136996263</v>
       </c>
       <c r="B122" t="n">
-        <v>80643</v>
+        <v>80648</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>136996264</v>
       </c>
       <c r="B123" t="n">
-        <v>80643</v>
+        <v>80648</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -16872,7 +16872,7 @@
         <v>136996265</v>
       </c>
       <c r="B124" t="n">
-        <v>80643</v>
+        <v>80648</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -17003,7 +17003,7 @@
         <v>136996266</v>
       </c>
       <c r="B125" t="n">
-        <v>80643</v>
+        <v>80648</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -17134,7 +17134,7 @@
         <v>136996267</v>
       </c>
       <c r="B126" t="n">
-        <v>80643</v>
+        <v>80648</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         <v>136996268</v>
       </c>
       <c r="B127" t="n">
-        <v>80643</v>
+        <v>80648</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -18626,7 +18626,7 @@
         <v>136996197</v>
       </c>
       <c r="B137" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>136996200</v>
       </c>
       <c r="B138" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -18891,7 +18891,7 @@
         <v>136996201</v>
       </c>
       <c r="B139" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -19015,7 +19015,7 @@
         <v>136996199</v>
       </c>
       <c r="B140" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>136996276</v>
       </c>
       <c r="B141" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>136996269</v>
       </c>
       <c r="B144" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         <v>136996270</v>
       </c>
       <c r="B145" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>136996271</v>
       </c>
       <c r="B146" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>136996274</v>
       </c>
       <c r="B147" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>136996275</v>
       </c>
       <c r="B148" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -20193,7 +20193,7 @@
         <v>136996278</v>
       </c>
       <c r="B150" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>136996279</v>
       </c>
       <c r="B151" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>136996282</v>
       </c>
       <c r="B152" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>136996283</v>
       </c>
       <c r="B153" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>136996221</v>
       </c>
       <c r="B154" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>

--- a/artfynd/A 17248-2026 artfynd.xlsx
+++ b/artfynd/A 17248-2026 artfynd.xlsx
@@ -19500,7 +19500,7 @@
         <v>136996269</v>
       </c>
       <c r="B144" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         <v>136996270</v>
       </c>
       <c r="B145" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>136996271</v>
       </c>
       <c r="B146" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>136996274</v>
       </c>
       <c r="B147" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>136996275</v>
       </c>
       <c r="B148" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>

--- a/artfynd/A 17248-2026 artfynd.xlsx
+++ b/artfynd/A 17248-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136996334</v>
       </c>
       <c r="B2" t="n">
-        <v>89528</v>
+        <v>89539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>136996333</v>
       </c>
       <c r="B3" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>136996220</v>
       </c>
       <c r="B4" t="n">
-        <v>80637</v>
+        <v>80648</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>136996284</v>
       </c>
       <c r="B22" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>136996285</v>
       </c>
       <c r="B23" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>136996286</v>
       </c>
       <c r="B24" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>136996287</v>
       </c>
       <c r="B25" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>136996288</v>
       </c>
       <c r="B26" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v>136996289</v>
       </c>
       <c r="B27" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>136996290</v>
       </c>
       <c r="B28" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>136996292</v>
       </c>
       <c r="B29" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>136996293</v>
       </c>
       <c r="B30" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>136996294</v>
       </c>
       <c r="B31" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>136996295</v>
       </c>
       <c r="B32" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>136996297</v>
       </c>
       <c r="B33" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>136996298</v>
       </c>
       <c r="B34" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>136996299</v>
       </c>
       <c r="B35" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>136996300</v>
       </c>
       <c r="B36" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>136996301</v>
       </c>
       <c r="B37" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         <v>136996302</v>
       </c>
       <c r="B38" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>136996303</v>
       </c>
       <c r="B39" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>136996304</v>
       </c>
       <c r="B40" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>136996305</v>
       </c>
       <c r="B41" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>136996306</v>
       </c>
       <c r="B42" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>136996307</v>
       </c>
       <c r="B43" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>136996308</v>
       </c>
       <c r="B44" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>136996309</v>
       </c>
       <c r="B45" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>136996310</v>
       </c>
       <c r="B46" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>136996311</v>
       </c>
       <c r="B47" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>136996313</v>
       </c>
       <c r="B48" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>136996314</v>
       </c>
       <c r="B49" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>136996315</v>
       </c>
       <c r="B50" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>136996316</v>
       </c>
       <c r="B51" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>136996317</v>
       </c>
       <c r="B52" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>136996318</v>
       </c>
       <c r="B53" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         <v>136996319</v>
       </c>
       <c r="B54" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         <v>136996320</v>
       </c>
       <c r="B55" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>136996321</v>
       </c>
       <c r="B56" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>136996322</v>
       </c>
       <c r="B57" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>136996323</v>
       </c>
       <c r="B58" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         <v>136996324</v>
       </c>
       <c r="B59" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>136996325</v>
       </c>
       <c r="B60" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>136996326</v>
       </c>
       <c r="B61" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>136996332</v>
       </c>
       <c r="B62" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>136996223</v>
       </c>
       <c r="B65" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9176,7 +9176,7 @@
         <v>136996224</v>
       </c>
       <c r="B66" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>136996225</v>
       </c>
       <c r="B67" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>136996226</v>
       </c>
       <c r="B68" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>136996228</v>
       </c>
       <c r="B69" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>136996229</v>
       </c>
       <c r="B70" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9851,7 +9851,7 @@
         <v>136996230</v>
       </c>
       <c r="B71" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>136996231</v>
       </c>
       <c r="B72" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -10118,7 +10118,7 @@
         <v>136996232</v>
       </c>
       <c r="B73" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>136996233</v>
       </c>
       <c r="B74" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>136996234</v>
       </c>
       <c r="B75" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>136996235</v>
       </c>
       <c r="B76" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>136996236</v>
       </c>
       <c r="B77" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         <v>136996237</v>
       </c>
       <c r="B78" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>136996239</v>
       </c>
       <c r="B79" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>136996240</v>
       </c>
       <c r="B80" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>136996241</v>
       </c>
       <c r="B81" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -11307,7 +11307,7 @@
         <v>136996242</v>
       </c>
       <c r="B82" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>136996243</v>
       </c>
       <c r="B83" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>136996244</v>
       </c>
       <c r="B84" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>136996245</v>
       </c>
       <c r="B85" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>136996246</v>
       </c>
       <c r="B86" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11977,7 +11977,7 @@
         <v>136996247</v>
       </c>
       <c r="B87" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>136996248</v>
       </c>
       <c r="B88" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -12249,7 +12249,7 @@
         <v>136996249</v>
       </c>
       <c r="B89" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>136996204</v>
       </c>
       <c r="B94" t="n">
-        <v>80641</v>
+        <v>80652</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -13034,7 +13034,7 @@
         <v>136996205</v>
       </c>
       <c r="B95" t="n">
-        <v>80641</v>
+        <v>80652</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -13165,7 +13165,7 @@
         <v>136996207</v>
       </c>
       <c r="B96" t="n">
-        <v>80641</v>
+        <v>80652</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -13296,7 +13296,7 @@
         <v>136996208</v>
       </c>
       <c r="B97" t="n">
-        <v>80641</v>
+        <v>80652</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>136996209</v>
       </c>
       <c r="B98" t="n">
-        <v>80641</v>
+        <v>80652</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
         <v>136996210</v>
       </c>
       <c r="B99" t="n">
-        <v>80641</v>
+        <v>80652</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>136996211</v>
       </c>
       <c r="B100" t="n">
-        <v>80641</v>
+        <v>80652</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>136996212</v>
       </c>
       <c r="B101" t="n">
-        <v>80641</v>
+        <v>80652</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>136996213</v>
       </c>
       <c r="B102" t="n">
-        <v>80641</v>
+        <v>80652</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -14082,7 +14082,7 @@
         <v>136996214</v>
       </c>
       <c r="B103" t="n">
-        <v>80641</v>
+        <v>80652</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>136996215</v>
       </c>
       <c r="B104" t="n">
-        <v>80641</v>
+        <v>80652</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>136996216</v>
       </c>
       <c r="B105" t="n">
-        <v>80641</v>
+        <v>80652</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>136996218</v>
       </c>
       <c r="B106" t="n">
-        <v>80641</v>
+        <v>80652</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>136996335</v>
       </c>
       <c r="B107" t="n">
-        <v>80647</v>
+        <v>80658</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>136996250</v>
       </c>
       <c r="B109" t="n">
-        <v>80648</v>
+        <v>80659</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>136996251</v>
       </c>
       <c r="B110" t="n">
-        <v>80648</v>
+        <v>80659</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>136996252</v>
       </c>
       <c r="B111" t="n">
-        <v>80648</v>
+        <v>80659</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
         <v>136996253</v>
       </c>
       <c r="B112" t="n">
-        <v>80648</v>
+        <v>80659</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>136996254</v>
       </c>
       <c r="B113" t="n">
-        <v>80648</v>
+        <v>80659</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -15542,7 +15542,7 @@
         <v>136996255</v>
       </c>
       <c r="B114" t="n">
-        <v>80648</v>
+        <v>80659</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>136996256</v>
       </c>
       <c r="B115" t="n">
-        <v>80648</v>
+        <v>80659</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>136996257</v>
       </c>
       <c r="B116" t="n">
-        <v>80648</v>
+        <v>80659</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -15935,7 +15935,7 @@
         <v>136996258</v>
       </c>
       <c r="B117" t="n">
-        <v>80648</v>
+        <v>80659</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -16071,7 +16071,7 @@
         <v>136996259</v>
       </c>
       <c r="B118" t="n">
-        <v>80648</v>
+        <v>80659</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>136996260</v>
       </c>
       <c r="B119" t="n">
-        <v>80648</v>
+        <v>80659</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -16333,7 +16333,7 @@
         <v>136996261</v>
       </c>
       <c r="B120" t="n">
-        <v>80648</v>
+        <v>80659</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
         <v>136996262</v>
       </c>
       <c r="B121" t="n">
-        <v>80648</v>
+        <v>80659</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -16600,7 +16600,7 @@
         <v>136996263</v>
       </c>
       <c r="B122" t="n">
-        <v>80648</v>
+        <v>80659</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>136996264</v>
       </c>
       <c r="B123" t="n">
-        <v>80648</v>
+        <v>80659</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -16872,7 +16872,7 @@
         <v>136996265</v>
       </c>
       <c r="B124" t="n">
-        <v>80648</v>
+        <v>80659</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -17003,7 +17003,7 @@
         <v>136996266</v>
       </c>
       <c r="B125" t="n">
-        <v>80648</v>
+        <v>80659</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -17134,7 +17134,7 @@
         <v>136996267</v>
       </c>
       <c r="B126" t="n">
-        <v>80648</v>
+        <v>80659</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         <v>136996268</v>
       </c>
       <c r="B127" t="n">
-        <v>80648</v>
+        <v>80659</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>136996269</v>
       </c>
       <c r="B144" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         <v>136996270</v>
       </c>
       <c r="B145" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>136996271</v>
       </c>
       <c r="B146" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>136996274</v>
       </c>
       <c r="B147" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>136996275</v>
       </c>
       <c r="B148" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -20193,7 +20193,7 @@
         <v>136996278</v>
       </c>
       <c r="B150" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>136996279</v>
       </c>
       <c r="B151" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>136996282</v>
       </c>
       <c r="B152" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>136996283</v>
       </c>
       <c r="B153" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>136996221</v>
       </c>
       <c r="B154" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>

--- a/artfynd/A 17248-2026 artfynd.xlsx
+++ b/artfynd/A 17248-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136996334</v>
       </c>
       <c r="B2" t="n">
-        <v>89539</v>
+        <v>89540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>136996333</v>
       </c>
       <c r="B3" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>136996220</v>
       </c>
       <c r="B4" t="n">
-        <v>80648</v>
+        <v>80649</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>136996284</v>
       </c>
       <c r="B22" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>136996285</v>
       </c>
       <c r="B23" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>136996286</v>
       </c>
       <c r="B24" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>136996287</v>
       </c>
       <c r="B25" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>136996288</v>
       </c>
       <c r="B26" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v>136996289</v>
       </c>
       <c r="B27" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>136996290</v>
       </c>
       <c r="B28" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>136996292</v>
       </c>
       <c r="B29" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>136996293</v>
       </c>
       <c r="B30" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>136996294</v>
       </c>
       <c r="B31" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>136996295</v>
       </c>
       <c r="B32" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>136996297</v>
       </c>
       <c r="B33" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>136996298</v>
       </c>
       <c r="B34" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>136996299</v>
       </c>
       <c r="B35" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>136996300</v>
       </c>
       <c r="B36" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>136996301</v>
       </c>
       <c r="B37" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         <v>136996302</v>
       </c>
       <c r="B38" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>136996303</v>
       </c>
       <c r="B39" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>136996304</v>
       </c>
       <c r="B40" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>136996305</v>
       </c>
       <c r="B41" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>136996306</v>
       </c>
       <c r="B42" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>136996307</v>
       </c>
       <c r="B43" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>136996308</v>
       </c>
       <c r="B44" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>136996309</v>
       </c>
       <c r="B45" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>136996310</v>
       </c>
       <c r="B46" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>136996311</v>
       </c>
       <c r="B47" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>136996313</v>
       </c>
       <c r="B48" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>136996314</v>
       </c>
       <c r="B49" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>136996315</v>
       </c>
       <c r="B50" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>136996316</v>
       </c>
       <c r="B51" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>136996317</v>
       </c>
       <c r="B52" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>136996318</v>
       </c>
       <c r="B53" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         <v>136996319</v>
       </c>
       <c r="B54" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         <v>136996320</v>
       </c>
       <c r="B55" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>136996321</v>
       </c>
       <c r="B56" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>136996322</v>
       </c>
       <c r="B57" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>136996323</v>
       </c>
       <c r="B58" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         <v>136996324</v>
       </c>
       <c r="B59" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>136996325</v>
       </c>
       <c r="B60" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>136996326</v>
       </c>
       <c r="B61" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>136996332</v>
       </c>
       <c r="B62" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>136996223</v>
       </c>
       <c r="B65" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9176,7 +9176,7 @@
         <v>136996224</v>
       </c>
       <c r="B66" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>136996225</v>
       </c>
       <c r="B67" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>136996226</v>
       </c>
       <c r="B68" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>136996228</v>
       </c>
       <c r="B69" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>136996229</v>
       </c>
       <c r="B70" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9851,7 +9851,7 @@
         <v>136996230</v>
       </c>
       <c r="B71" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>136996231</v>
       </c>
       <c r="B72" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -10118,7 +10118,7 @@
         <v>136996232</v>
       </c>
       <c r="B73" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>136996233</v>
       </c>
       <c r="B74" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>136996234</v>
       </c>
       <c r="B75" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>136996235</v>
       </c>
       <c r="B76" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>136996236</v>
       </c>
       <c r="B77" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         <v>136996237</v>
       </c>
       <c r="B78" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>136996239</v>
       </c>
       <c r="B79" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>136996240</v>
       </c>
       <c r="B80" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>136996241</v>
       </c>
       <c r="B81" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -11307,7 +11307,7 @@
         <v>136996242</v>
       </c>
       <c r="B82" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>136996243</v>
       </c>
       <c r="B83" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>136996244</v>
       </c>
       <c r="B84" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>136996245</v>
       </c>
       <c r="B85" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>136996246</v>
       </c>
       <c r="B86" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11977,7 +11977,7 @@
         <v>136996247</v>
       </c>
       <c r="B87" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>136996248</v>
       </c>
       <c r="B88" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -12249,7 +12249,7 @@
         <v>136996249</v>
       </c>
       <c r="B89" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>136996204</v>
       </c>
       <c r="B94" t="n">
-        <v>80652</v>
+        <v>80653</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -13034,7 +13034,7 @@
         <v>136996205</v>
       </c>
       <c r="B95" t="n">
-        <v>80652</v>
+        <v>80653</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -13165,7 +13165,7 @@
         <v>136996207</v>
       </c>
       <c r="B96" t="n">
-        <v>80652</v>
+        <v>80653</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -13296,7 +13296,7 @@
         <v>136996208</v>
       </c>
       <c r="B97" t="n">
-        <v>80652</v>
+        <v>80653</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>136996209</v>
       </c>
       <c r="B98" t="n">
-        <v>80652</v>
+        <v>80653</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
         <v>136996210</v>
       </c>
       <c r="B99" t="n">
-        <v>80652</v>
+        <v>80653</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>136996211</v>
       </c>
       <c r="B100" t="n">
-        <v>80652</v>
+        <v>80653</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>136996212</v>
       </c>
       <c r="B101" t="n">
-        <v>80652</v>
+        <v>80653</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>136996213</v>
       </c>
       <c r="B102" t="n">
-        <v>80652</v>
+        <v>80653</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -14082,7 +14082,7 @@
         <v>136996214</v>
       </c>
       <c r="B103" t="n">
-        <v>80652</v>
+        <v>80653</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>136996215</v>
       </c>
       <c r="B104" t="n">
-        <v>80652</v>
+        <v>80653</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>136996216</v>
       </c>
       <c r="B105" t="n">
-        <v>80652</v>
+        <v>80653</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>136996218</v>
       </c>
       <c r="B106" t="n">
-        <v>80652</v>
+        <v>80653</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>136996335</v>
       </c>
       <c r="B107" t="n">
-        <v>80658</v>
+        <v>80659</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>136996250</v>
       </c>
       <c r="B109" t="n">
-        <v>80659</v>
+        <v>80660</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>136996251</v>
       </c>
       <c r="B110" t="n">
-        <v>80659</v>
+        <v>80660</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>136996252</v>
       </c>
       <c r="B111" t="n">
-        <v>80659</v>
+        <v>80660</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
         <v>136996253</v>
       </c>
       <c r="B112" t="n">
-        <v>80659</v>
+        <v>80660</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>136996254</v>
       </c>
       <c r="B113" t="n">
-        <v>80659</v>
+        <v>80660</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -15542,7 +15542,7 @@
         <v>136996255</v>
       </c>
       <c r="B114" t="n">
-        <v>80659</v>
+        <v>80660</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>136996256</v>
       </c>
       <c r="B115" t="n">
-        <v>80659</v>
+        <v>80660</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>136996257</v>
       </c>
       <c r="B116" t="n">
-        <v>80659</v>
+        <v>80660</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -15935,7 +15935,7 @@
         <v>136996258</v>
       </c>
       <c r="B117" t="n">
-        <v>80659</v>
+        <v>80660</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -16071,7 +16071,7 @@
         <v>136996259</v>
       </c>
       <c r="B118" t="n">
-        <v>80659</v>
+        <v>80660</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>136996260</v>
       </c>
       <c r="B119" t="n">
-        <v>80659</v>
+        <v>80660</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -16333,7 +16333,7 @@
         <v>136996261</v>
       </c>
       <c r="B120" t="n">
-        <v>80659</v>
+        <v>80660</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
         <v>136996262</v>
       </c>
       <c r="B121" t="n">
-        <v>80659</v>
+        <v>80660</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -16600,7 +16600,7 @@
         <v>136996263</v>
       </c>
       <c r="B122" t="n">
-        <v>80659</v>
+        <v>80660</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>136996264</v>
       </c>
       <c r="B123" t="n">
-        <v>80659</v>
+        <v>80660</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -16872,7 +16872,7 @@
         <v>136996265</v>
       </c>
       <c r="B124" t="n">
-        <v>80659</v>
+        <v>80660</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -17003,7 +17003,7 @@
         <v>136996266</v>
       </c>
       <c r="B125" t="n">
-        <v>80659</v>
+        <v>80660</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -17134,7 +17134,7 @@
         <v>136996267</v>
       </c>
       <c r="B126" t="n">
-        <v>80659</v>
+        <v>80660</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         <v>136996268</v>
       </c>
       <c r="B127" t="n">
-        <v>80659</v>
+        <v>80660</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>136996269</v>
       </c>
       <c r="B144" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         <v>136996270</v>
       </c>
       <c r="B145" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>136996271</v>
       </c>
       <c r="B146" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>136996274</v>
       </c>
       <c r="B147" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>136996275</v>
       </c>
       <c r="B148" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -20193,7 +20193,7 @@
         <v>136996278</v>
       </c>
       <c r="B150" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>136996279</v>
       </c>
       <c r="B151" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>136996282</v>
       </c>
       <c r="B152" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>136996283</v>
       </c>
       <c r="B153" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>136996221</v>
       </c>
       <c r="B154" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>

--- a/artfynd/A 17248-2026 artfynd.xlsx
+++ b/artfynd/A 17248-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136996334</v>
       </c>
       <c r="B2" t="n">
-        <v>89540</v>
+        <v>89543</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>136996333</v>
       </c>
       <c r="B3" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>136996220</v>
       </c>
       <c r="B4" t="n">
-        <v>80649</v>
+        <v>80651</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>136996284</v>
       </c>
       <c r="B22" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>136996285</v>
       </c>
       <c r="B23" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>136996286</v>
       </c>
       <c r="B24" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>136996287</v>
       </c>
       <c r="B25" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>136996288</v>
       </c>
       <c r="B26" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v>136996289</v>
       </c>
       <c r="B27" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>136996290</v>
       </c>
       <c r="B28" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>136996292</v>
       </c>
       <c r="B29" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>136996293</v>
       </c>
       <c r="B30" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>136996294</v>
       </c>
       <c r="B31" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>136996295</v>
       </c>
       <c r="B32" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>136996297</v>
       </c>
       <c r="B33" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>136996298</v>
       </c>
       <c r="B34" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>136996299</v>
       </c>
       <c r="B35" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>136996300</v>
       </c>
       <c r="B36" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>136996301</v>
       </c>
       <c r="B37" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         <v>136996302</v>
       </c>
       <c r="B38" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>136996303</v>
       </c>
       <c r="B39" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>136996304</v>
       </c>
       <c r="B40" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>136996305</v>
       </c>
       <c r="B41" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>136996306</v>
       </c>
       <c r="B42" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>136996307</v>
       </c>
       <c r="B43" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>136996308</v>
       </c>
       <c r="B44" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>136996309</v>
       </c>
       <c r="B45" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>136996310</v>
       </c>
       <c r="B46" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>136996311</v>
       </c>
       <c r="B47" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>136996313</v>
       </c>
       <c r="B48" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>136996314</v>
       </c>
       <c r="B49" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>136996315</v>
       </c>
       <c r="B50" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>136996316</v>
       </c>
       <c r="B51" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>136996317</v>
       </c>
       <c r="B52" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>136996318</v>
       </c>
       <c r="B53" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         <v>136996319</v>
       </c>
       <c r="B54" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         <v>136996320</v>
       </c>
       <c r="B55" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>136996321</v>
       </c>
       <c r="B56" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>136996322</v>
       </c>
       <c r="B57" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>136996323</v>
       </c>
       <c r="B58" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         <v>136996324</v>
       </c>
       <c r="B59" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>136996325</v>
       </c>
       <c r="B60" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>136996326</v>
       </c>
       <c r="B61" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>136996332</v>
       </c>
       <c r="B62" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>136996223</v>
       </c>
       <c r="B65" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9176,7 +9176,7 @@
         <v>136996224</v>
       </c>
       <c r="B66" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>136996225</v>
       </c>
       <c r="B67" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>136996226</v>
       </c>
       <c r="B68" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>136996228</v>
       </c>
       <c r="B69" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>136996229</v>
       </c>
       <c r="B70" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9851,7 +9851,7 @@
         <v>136996230</v>
       </c>
       <c r="B71" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>136996231</v>
       </c>
       <c r="B72" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -10118,7 +10118,7 @@
         <v>136996232</v>
       </c>
       <c r="B73" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>136996233</v>
       </c>
       <c r="B74" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>136996234</v>
       </c>
       <c r="B75" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>136996235</v>
       </c>
       <c r="B76" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>136996236</v>
       </c>
       <c r="B77" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         <v>136996237</v>
       </c>
       <c r="B78" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>136996239</v>
       </c>
       <c r="B79" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>136996240</v>
       </c>
       <c r="B80" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>136996241</v>
       </c>
       <c r="B81" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -11307,7 +11307,7 @@
         <v>136996242</v>
       </c>
       <c r="B82" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>136996243</v>
       </c>
       <c r="B83" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>136996244</v>
       </c>
       <c r="B84" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>136996245</v>
       </c>
       <c r="B85" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>136996246</v>
       </c>
       <c r="B86" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11977,7 +11977,7 @@
         <v>136996247</v>
       </c>
       <c r="B87" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>136996248</v>
       </c>
       <c r="B88" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -12249,7 +12249,7 @@
         <v>136996249</v>
       </c>
       <c r="B89" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>136996204</v>
       </c>
       <c r="B94" t="n">
-        <v>80653</v>
+        <v>80655</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -13034,7 +13034,7 @@
         <v>136996205</v>
       </c>
       <c r="B95" t="n">
-        <v>80653</v>
+        <v>80655</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -13165,7 +13165,7 @@
         <v>136996207</v>
       </c>
       <c r="B96" t="n">
-        <v>80653</v>
+        <v>80655</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -13296,7 +13296,7 @@
         <v>136996208</v>
       </c>
       <c r="B97" t="n">
-        <v>80653</v>
+        <v>80655</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>136996209</v>
       </c>
       <c r="B98" t="n">
-        <v>80653</v>
+        <v>80655</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
         <v>136996210</v>
       </c>
       <c r="B99" t="n">
-        <v>80653</v>
+        <v>80655</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>136996211</v>
       </c>
       <c r="B100" t="n">
-        <v>80653</v>
+        <v>80655</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>136996212</v>
       </c>
       <c r="B101" t="n">
-        <v>80653</v>
+        <v>80655</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>136996213</v>
       </c>
       <c r="B102" t="n">
-        <v>80653</v>
+        <v>80655</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -14082,7 +14082,7 @@
         <v>136996214</v>
       </c>
       <c r="B103" t="n">
-        <v>80653</v>
+        <v>80655</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>136996215</v>
       </c>
       <c r="B104" t="n">
-        <v>80653</v>
+        <v>80655</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>136996216</v>
       </c>
       <c r="B105" t="n">
-        <v>80653</v>
+        <v>80655</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>136996218</v>
       </c>
       <c r="B106" t="n">
-        <v>80653</v>
+        <v>80655</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>136996335</v>
       </c>
       <c r="B107" t="n">
-        <v>80659</v>
+        <v>80661</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>136996250</v>
       </c>
       <c r="B109" t="n">
-        <v>80660</v>
+        <v>80662</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>136996251</v>
       </c>
       <c r="B110" t="n">
-        <v>80660</v>
+        <v>80662</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>136996252</v>
       </c>
       <c r="B111" t="n">
-        <v>80660</v>
+        <v>80662</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
         <v>136996253</v>
       </c>
       <c r="B112" t="n">
-        <v>80660</v>
+        <v>80662</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>136996254</v>
       </c>
       <c r="B113" t="n">
-        <v>80660</v>
+        <v>80662</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -15542,7 +15542,7 @@
         <v>136996255</v>
       </c>
       <c r="B114" t="n">
-        <v>80660</v>
+        <v>80662</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>136996256</v>
       </c>
       <c r="B115" t="n">
-        <v>80660</v>
+        <v>80662</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>136996257</v>
       </c>
       <c r="B116" t="n">
-        <v>80660</v>
+        <v>80662</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -15935,7 +15935,7 @@
         <v>136996258</v>
       </c>
       <c r="B117" t="n">
-        <v>80660</v>
+        <v>80662</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -16071,7 +16071,7 @@
         <v>136996259</v>
       </c>
       <c r="B118" t="n">
-        <v>80660</v>
+        <v>80662</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>136996260</v>
       </c>
       <c r="B119" t="n">
-        <v>80660</v>
+        <v>80662</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -16333,7 +16333,7 @@
         <v>136996261</v>
       </c>
       <c r="B120" t="n">
-        <v>80660</v>
+        <v>80662</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
         <v>136996262</v>
       </c>
       <c r="B121" t="n">
-        <v>80660</v>
+        <v>80662</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -16600,7 +16600,7 @@
         <v>136996263</v>
       </c>
       <c r="B122" t="n">
-        <v>80660</v>
+        <v>80662</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>136996264</v>
       </c>
       <c r="B123" t="n">
-        <v>80660</v>
+        <v>80662</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -16872,7 +16872,7 @@
         <v>136996265</v>
       </c>
       <c r="B124" t="n">
-        <v>80660</v>
+        <v>80662</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -17003,7 +17003,7 @@
         <v>136996266</v>
       </c>
       <c r="B125" t="n">
-        <v>80660</v>
+        <v>80662</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -17134,7 +17134,7 @@
         <v>136996267</v>
       </c>
       <c r="B126" t="n">
-        <v>80660</v>
+        <v>80662</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         <v>136996268</v>
       </c>
       <c r="B127" t="n">
-        <v>80660</v>
+        <v>80662</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>136996269</v>
       </c>
       <c r="B144" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         <v>136996270</v>
       </c>
       <c r="B145" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>136996271</v>
       </c>
       <c r="B146" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>136996274</v>
       </c>
       <c r="B147" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>136996275</v>
       </c>
       <c r="B148" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -20193,7 +20193,7 @@
         <v>136996278</v>
       </c>
       <c r="B150" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>136996279</v>
       </c>
       <c r="B151" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>136996282</v>
       </c>
       <c r="B152" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>136996283</v>
       </c>
       <c r="B153" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>136996221</v>
       </c>
       <c r="B154" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>

--- a/artfynd/A 17248-2026 artfynd.xlsx
+++ b/artfynd/A 17248-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136996334</v>
       </c>
       <c r="B2" t="n">
-        <v>89543</v>
+        <v>89544</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>136996333</v>
       </c>
       <c r="B3" t="n">
-        <v>83403</v>
+        <v>83404</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>136996220</v>
       </c>
       <c r="B4" t="n">
-        <v>80651</v>
+        <v>80652</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>136996284</v>
       </c>
       <c r="B22" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>136996285</v>
       </c>
       <c r="B23" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>136996286</v>
       </c>
       <c r="B24" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>136996287</v>
       </c>
       <c r="B25" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>136996288</v>
       </c>
       <c r="B26" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v>136996289</v>
       </c>
       <c r="B27" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>136996290</v>
       </c>
       <c r="B28" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>136996292</v>
       </c>
       <c r="B29" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>136996293</v>
       </c>
       <c r="B30" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>136996294</v>
       </c>
       <c r="B31" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>136996295</v>
       </c>
       <c r="B32" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>136996297</v>
       </c>
       <c r="B33" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>136996298</v>
       </c>
       <c r="B34" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>136996299</v>
       </c>
       <c r="B35" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>136996300</v>
       </c>
       <c r="B36" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>136996301</v>
       </c>
       <c r="B37" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         <v>136996302</v>
       </c>
       <c r="B38" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>136996303</v>
       </c>
       <c r="B39" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>136996304</v>
       </c>
       <c r="B40" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>136996305</v>
       </c>
       <c r="B41" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>136996306</v>
       </c>
       <c r="B42" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>136996307</v>
       </c>
       <c r="B43" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>136996308</v>
       </c>
       <c r="B44" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>136996309</v>
       </c>
       <c r="B45" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>136996310</v>
       </c>
       <c r="B46" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>136996311</v>
       </c>
       <c r="B47" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>136996313</v>
       </c>
       <c r="B48" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>136996314</v>
       </c>
       <c r="B49" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>136996315</v>
       </c>
       <c r="B50" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>136996316</v>
       </c>
       <c r="B51" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>136996317</v>
       </c>
       <c r="B52" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>136996318</v>
       </c>
       <c r="B53" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         <v>136996319</v>
       </c>
       <c r="B54" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         <v>136996320</v>
       </c>
       <c r="B55" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>136996321</v>
       </c>
       <c r="B56" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>136996322</v>
       </c>
       <c r="B57" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>136996323</v>
       </c>
       <c r="B58" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         <v>136996324</v>
       </c>
       <c r="B59" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>136996325</v>
       </c>
       <c r="B60" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>136996326</v>
       </c>
       <c r="B61" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>136996332</v>
       </c>
       <c r="B62" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>136996223</v>
       </c>
       <c r="B65" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9176,7 +9176,7 @@
         <v>136996224</v>
       </c>
       <c r="B66" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>136996225</v>
       </c>
       <c r="B67" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>136996226</v>
       </c>
       <c r="B68" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>136996228</v>
       </c>
       <c r="B69" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>136996229</v>
       </c>
       <c r="B70" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9851,7 +9851,7 @@
         <v>136996230</v>
       </c>
       <c r="B71" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>136996231</v>
       </c>
       <c r="B72" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -10118,7 +10118,7 @@
         <v>136996232</v>
       </c>
       <c r="B73" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>136996233</v>
       </c>
       <c r="B74" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>136996234</v>
       </c>
       <c r="B75" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>136996235</v>
       </c>
       <c r="B76" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>136996236</v>
       </c>
       <c r="B77" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         <v>136996237</v>
       </c>
       <c r="B78" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>136996239</v>
       </c>
       <c r="B79" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>136996240</v>
       </c>
       <c r="B80" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>136996241</v>
       </c>
       <c r="B81" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -11307,7 +11307,7 @@
         <v>136996242</v>
       </c>
       <c r="B82" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>136996243</v>
       </c>
       <c r="B83" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>136996244</v>
       </c>
       <c r="B84" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>136996245</v>
       </c>
       <c r="B85" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>136996246</v>
       </c>
       <c r="B86" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11977,7 +11977,7 @@
         <v>136996247</v>
       </c>
       <c r="B87" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>136996248</v>
       </c>
       <c r="B88" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -12249,7 +12249,7 @@
         <v>136996249</v>
       </c>
       <c r="B89" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>136996204</v>
       </c>
       <c r="B94" t="n">
-        <v>80655</v>
+        <v>80656</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -13034,7 +13034,7 @@
         <v>136996205</v>
       </c>
       <c r="B95" t="n">
-        <v>80655</v>
+        <v>80656</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -13165,7 +13165,7 @@
         <v>136996207</v>
       </c>
       <c r="B96" t="n">
-        <v>80655</v>
+        <v>80656</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -13296,7 +13296,7 @@
         <v>136996208</v>
       </c>
       <c r="B97" t="n">
-        <v>80655</v>
+        <v>80656</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>136996209</v>
       </c>
       <c r="B98" t="n">
-        <v>80655</v>
+        <v>80656</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
         <v>136996210</v>
       </c>
       <c r="B99" t="n">
-        <v>80655</v>
+        <v>80656</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>136996211</v>
       </c>
       <c r="B100" t="n">
-        <v>80655</v>
+        <v>80656</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>136996212</v>
       </c>
       <c r="B101" t="n">
-        <v>80655</v>
+        <v>80656</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>136996213</v>
       </c>
       <c r="B102" t="n">
-        <v>80655</v>
+        <v>80656</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -14082,7 +14082,7 @@
         <v>136996214</v>
       </c>
       <c r="B103" t="n">
-        <v>80655</v>
+        <v>80656</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>136996215</v>
       </c>
       <c r="B104" t="n">
-        <v>80655</v>
+        <v>80656</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>136996216</v>
       </c>
       <c r="B105" t="n">
-        <v>80655</v>
+        <v>80656</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>136996218</v>
       </c>
       <c r="B106" t="n">
-        <v>80655</v>
+        <v>80656</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>136996335</v>
       </c>
       <c r="B107" t="n">
-        <v>80661</v>
+        <v>80662</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>136996250</v>
       </c>
       <c r="B109" t="n">
-        <v>80662</v>
+        <v>80663</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>136996251</v>
       </c>
       <c r="B110" t="n">
-        <v>80662</v>
+        <v>80663</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>136996252</v>
       </c>
       <c r="B111" t="n">
-        <v>80662</v>
+        <v>80663</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
         <v>136996253</v>
       </c>
       <c r="B112" t="n">
-        <v>80662</v>
+        <v>80663</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>136996254</v>
       </c>
       <c r="B113" t="n">
-        <v>80662</v>
+        <v>80663</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -15542,7 +15542,7 @@
         <v>136996255</v>
       </c>
       <c r="B114" t="n">
-        <v>80662</v>
+        <v>80663</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>136996256</v>
       </c>
       <c r="B115" t="n">
-        <v>80662</v>
+        <v>80663</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>136996257</v>
       </c>
       <c r="B116" t="n">
-        <v>80662</v>
+        <v>80663</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -15935,7 +15935,7 @@
         <v>136996258</v>
       </c>
       <c r="B117" t="n">
-        <v>80662</v>
+        <v>80663</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -16071,7 +16071,7 @@
         <v>136996259</v>
       </c>
       <c r="B118" t="n">
-        <v>80662</v>
+        <v>80663</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>136996260</v>
       </c>
       <c r="B119" t="n">
-        <v>80662</v>
+        <v>80663</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -16333,7 +16333,7 @@
         <v>136996261</v>
       </c>
       <c r="B120" t="n">
-        <v>80662</v>
+        <v>80663</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
         <v>136996262</v>
       </c>
       <c r="B121" t="n">
-        <v>80662</v>
+        <v>80663</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -16600,7 +16600,7 @@
         <v>136996263</v>
       </c>
       <c r="B122" t="n">
-        <v>80662</v>
+        <v>80663</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>136996264</v>
       </c>
       <c r="B123" t="n">
-        <v>80662</v>
+        <v>80663</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -16872,7 +16872,7 @@
         <v>136996265</v>
       </c>
       <c r="B124" t="n">
-        <v>80662</v>
+        <v>80663</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -17003,7 +17003,7 @@
         <v>136996266</v>
       </c>
       <c r="B125" t="n">
-        <v>80662</v>
+        <v>80663</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -17134,7 +17134,7 @@
         <v>136996267</v>
       </c>
       <c r="B126" t="n">
-        <v>80662</v>
+        <v>80663</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         <v>136996268</v>
       </c>
       <c r="B127" t="n">
-        <v>80662</v>
+        <v>80663</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>136996269</v>
       </c>
       <c r="B144" t="n">
-        <v>111430</v>
+        <v>111432</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         <v>136996270</v>
       </c>
       <c r="B145" t="n">
-        <v>111430</v>
+        <v>111432</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>136996271</v>
       </c>
       <c r="B146" t="n">
-        <v>111430</v>
+        <v>111432</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>136996274</v>
       </c>
       <c r="B147" t="n">
-        <v>111430</v>
+        <v>111432</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>136996275</v>
       </c>
       <c r="B148" t="n">
-        <v>111430</v>
+        <v>111432</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -20193,7 +20193,7 @@
         <v>136996278</v>
       </c>
       <c r="B150" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>136996279</v>
       </c>
       <c r="B151" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>136996282</v>
       </c>
       <c r="B152" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>136996283</v>
       </c>
       <c r="B153" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>136996221</v>
       </c>
       <c r="B154" t="n">
-        <v>98296</v>
+        <v>98297</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>

--- a/artfynd/A 17248-2026 artfynd.xlsx
+++ b/artfynd/A 17248-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136996334</v>
       </c>
       <c r="B2" t="n">
-        <v>89544</v>
+        <v>89547</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>136996333</v>
       </c>
       <c r="B3" t="n">
-        <v>83404</v>
+        <v>83407</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>136996220</v>
       </c>
       <c r="B4" t="n">
-        <v>80652</v>
+        <v>80655</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>136996284</v>
       </c>
       <c r="B22" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>136996285</v>
       </c>
       <c r="B23" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>136996286</v>
       </c>
       <c r="B24" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>136996287</v>
       </c>
       <c r="B25" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>136996288</v>
       </c>
       <c r="B26" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v>136996289</v>
       </c>
       <c r="B27" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>136996290</v>
       </c>
       <c r="B28" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>136996292</v>
       </c>
       <c r="B29" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>136996293</v>
       </c>
       <c r="B30" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>136996294</v>
       </c>
       <c r="B31" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>136996295</v>
       </c>
       <c r="B32" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>136996297</v>
       </c>
       <c r="B33" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>136996298</v>
       </c>
       <c r="B34" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>136996299</v>
       </c>
       <c r="B35" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>136996300</v>
       </c>
       <c r="B36" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>136996301</v>
       </c>
       <c r="B37" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         <v>136996302</v>
       </c>
       <c r="B38" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>136996303</v>
       </c>
       <c r="B39" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>136996304</v>
       </c>
       <c r="B40" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>136996305</v>
       </c>
       <c r="B41" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>136996306</v>
       </c>
       <c r="B42" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>136996307</v>
       </c>
       <c r="B43" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>136996308</v>
       </c>
       <c r="B44" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>136996309</v>
       </c>
       <c r="B45" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>136996310</v>
       </c>
       <c r="B46" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>136996311</v>
       </c>
       <c r="B47" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>136996313</v>
       </c>
       <c r="B48" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>136996314</v>
       </c>
       <c r="B49" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>136996315</v>
       </c>
       <c r="B50" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>136996316</v>
       </c>
       <c r="B51" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>136996317</v>
       </c>
       <c r="B52" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>136996318</v>
       </c>
       <c r="B53" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         <v>136996319</v>
       </c>
       <c r="B54" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         <v>136996320</v>
       </c>
       <c r="B55" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>136996321</v>
       </c>
       <c r="B56" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>136996322</v>
       </c>
       <c r="B57" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>136996323</v>
       </c>
       <c r="B58" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         <v>136996324</v>
       </c>
       <c r="B59" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>136996325</v>
       </c>
       <c r="B60" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>136996326</v>
       </c>
       <c r="B61" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>136996332</v>
       </c>
       <c r="B62" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>136996223</v>
       </c>
       <c r="B65" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9176,7 +9176,7 @@
         <v>136996224</v>
       </c>
       <c r="B66" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>136996225</v>
       </c>
       <c r="B67" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>136996226</v>
       </c>
       <c r="B68" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>136996228</v>
       </c>
       <c r="B69" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>136996229</v>
       </c>
       <c r="B70" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9851,7 +9851,7 @@
         <v>136996230</v>
       </c>
       <c r="B71" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>136996231</v>
       </c>
       <c r="B72" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -10118,7 +10118,7 @@
         <v>136996232</v>
       </c>
       <c r="B73" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>136996233</v>
       </c>
       <c r="B74" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>136996234</v>
       </c>
       <c r="B75" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>136996235</v>
       </c>
       <c r="B76" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>136996236</v>
       </c>
       <c r="B77" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         <v>136996237</v>
       </c>
       <c r="B78" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>136996239</v>
       </c>
       <c r="B79" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>136996240</v>
       </c>
       <c r="B80" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>136996241</v>
       </c>
       <c r="B81" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -11307,7 +11307,7 @@
         <v>136996242</v>
       </c>
       <c r="B82" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>136996243</v>
       </c>
       <c r="B83" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>136996244</v>
       </c>
       <c r="B84" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>136996245</v>
       </c>
       <c r="B85" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>136996246</v>
       </c>
       <c r="B86" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11977,7 +11977,7 @@
         <v>136996247</v>
       </c>
       <c r="B87" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>136996248</v>
       </c>
       <c r="B88" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -12249,7 +12249,7 @@
         <v>136996249</v>
       </c>
       <c r="B89" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>136996204</v>
       </c>
       <c r="B94" t="n">
-        <v>80656</v>
+        <v>80659</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -13034,7 +13034,7 @@
         <v>136996205</v>
       </c>
       <c r="B95" t="n">
-        <v>80656</v>
+        <v>80659</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -13165,7 +13165,7 @@
         <v>136996207</v>
       </c>
       <c r="B96" t="n">
-        <v>80656</v>
+        <v>80659</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -13296,7 +13296,7 @@
         <v>136996208</v>
       </c>
       <c r="B97" t="n">
-        <v>80656</v>
+        <v>80659</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>136996209</v>
       </c>
       <c r="B98" t="n">
-        <v>80656</v>
+        <v>80659</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
         <v>136996210</v>
       </c>
       <c r="B99" t="n">
-        <v>80656</v>
+        <v>80659</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>136996211</v>
       </c>
       <c r="B100" t="n">
-        <v>80656</v>
+        <v>80659</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>136996212</v>
       </c>
       <c r="B101" t="n">
-        <v>80656</v>
+        <v>80659</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>136996213</v>
       </c>
       <c r="B102" t="n">
-        <v>80656</v>
+        <v>80659</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -14082,7 +14082,7 @@
         <v>136996214</v>
       </c>
       <c r="B103" t="n">
-        <v>80656</v>
+        <v>80659</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>136996215</v>
       </c>
       <c r="B104" t="n">
-        <v>80656</v>
+        <v>80659</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>136996216</v>
       </c>
       <c r="B105" t="n">
-        <v>80656</v>
+        <v>80659</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>136996218</v>
       </c>
       <c r="B106" t="n">
-        <v>80656</v>
+        <v>80659</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>136996335</v>
       </c>
       <c r="B107" t="n">
-        <v>80662</v>
+        <v>80665</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>136996250</v>
       </c>
       <c r="B109" t="n">
-        <v>80663</v>
+        <v>80666</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>136996251</v>
       </c>
       <c r="B110" t="n">
-        <v>80663</v>
+        <v>80666</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>136996252</v>
       </c>
       <c r="B111" t="n">
-        <v>80663</v>
+        <v>80666</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
         <v>136996253</v>
       </c>
       <c r="B112" t="n">
-        <v>80663</v>
+        <v>80666</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>136996254</v>
       </c>
       <c r="B113" t="n">
-        <v>80663</v>
+        <v>80666</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -15542,7 +15542,7 @@
         <v>136996255</v>
       </c>
       <c r="B114" t="n">
-        <v>80663</v>
+        <v>80666</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>136996256</v>
       </c>
       <c r="B115" t="n">
-        <v>80663</v>
+        <v>80666</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>136996257</v>
       </c>
       <c r="B116" t="n">
-        <v>80663</v>
+        <v>80666</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -15935,7 +15935,7 @@
         <v>136996258</v>
       </c>
       <c r="B117" t="n">
-        <v>80663</v>
+        <v>80666</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -16071,7 +16071,7 @@
         <v>136996259</v>
       </c>
       <c r="B118" t="n">
-        <v>80663</v>
+        <v>80666</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>136996260</v>
       </c>
       <c r="B119" t="n">
-        <v>80663</v>
+        <v>80666</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -16333,7 +16333,7 @@
         <v>136996261</v>
       </c>
       <c r="B120" t="n">
-        <v>80663</v>
+        <v>80666</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
         <v>136996262</v>
       </c>
       <c r="B121" t="n">
-        <v>80663</v>
+        <v>80666</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -16600,7 +16600,7 @@
         <v>136996263</v>
       </c>
       <c r="B122" t="n">
-        <v>80663</v>
+        <v>80666</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>136996264</v>
       </c>
       <c r="B123" t="n">
-        <v>80663</v>
+        <v>80666</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -16872,7 +16872,7 @@
         <v>136996265</v>
       </c>
       <c r="B124" t="n">
-        <v>80663</v>
+        <v>80666</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -17003,7 +17003,7 @@
         <v>136996266</v>
       </c>
       <c r="B125" t="n">
-        <v>80663</v>
+        <v>80666</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -17134,7 +17134,7 @@
         <v>136996267</v>
       </c>
       <c r="B126" t="n">
-        <v>80663</v>
+        <v>80666</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         <v>136996268</v>
       </c>
       <c r="B127" t="n">
-        <v>80663</v>
+        <v>80666</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -18626,7 +18626,7 @@
         <v>136996197</v>
       </c>
       <c r="B137" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>136996200</v>
       </c>
       <c r="B138" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -18891,7 +18891,7 @@
         <v>136996201</v>
       </c>
       <c r="B139" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -19015,7 +19015,7 @@
         <v>136996199</v>
       </c>
       <c r="B140" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>136996276</v>
       </c>
       <c r="B141" t="n">
-        <v>58139</v>
+        <v>58142</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>136996269</v>
       </c>
       <c r="B144" t="n">
-        <v>111432</v>
+        <v>111436</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         <v>136996270</v>
       </c>
       <c r="B145" t="n">
-        <v>111432</v>
+        <v>111436</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>136996271</v>
       </c>
       <c r="B146" t="n">
-        <v>111432</v>
+        <v>111436</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>136996274</v>
       </c>
       <c r="B147" t="n">
-        <v>111432</v>
+        <v>111436</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>136996275</v>
       </c>
       <c r="B148" t="n">
-        <v>111432</v>
+        <v>111436</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -20193,7 +20193,7 @@
         <v>136996278</v>
       </c>
       <c r="B150" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>136996279</v>
       </c>
       <c r="B151" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>136996282</v>
       </c>
       <c r="B152" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>136996283</v>
       </c>
       <c r="B153" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>136996221</v>
       </c>
       <c r="B154" t="n">
-        <v>98297</v>
+        <v>98300</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
